--- a/.claude/raw_document/IMQuestionnaire.xlsx
+++ b/.claude/raw_document/IMQuestionnaire.xlsx
@@ -5,12 +5,12 @@
   <workbookPr saveExternalLinkValues="0" updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sara\Downloads\AIagentproject\raw_document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sara\Downloads\AIagentproject\.claude\raw_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18185A95-624A-4173-AD19-6D2684435BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B9F7B0-F4A3-4134-BDD5-258D1B6A9314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" tabRatio="709" activeTab="3" xr2:uid="{9ADBD64C-0D47-4706-82F2-7295FAAD6BE3}"/>
+    <workbookView xWindow="35055" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="709" activeTab="2" xr2:uid="{9ADBD64C-0D47-4706-82F2-7295FAAD6BE3}"/>
   </bookViews>
   <sheets>
     <sheet name="IM Info" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="265">
   <si>
     <t>Australian Business Number (ABN)</t>
   </si>
@@ -434,9 +434,6 @@
     <t>iShares Enhanced Moderate</t>
   </si>
   <si>
-    <t>iShare Enhanced Strategic Conservative</t>
-  </si>
-  <si>
     <t>iShares Enhanced Balanced</t>
   </si>
   <si>
@@ -446,9 +443,6 @@
     <t>iShares Enhanced Aggressive</t>
   </si>
   <si>
-    <t>iShares Enhanced All Grwoth</t>
-  </si>
-  <si>
     <t>Asset Class</t>
   </si>
   <si>
@@ -746,9 +740,6 @@
     <t>To match or outperform the benchmark over a rolling five-year period</t>
   </si>
   <si>
-    <t>ETF Portfolio</t>
-  </si>
-  <si>
     <t>Normal Market</t>
   </si>
   <si>
@@ -791,9 +782,6 @@
     <t>Morningstar Growth</t>
   </si>
   <si>
-    <t>iShares All Growth</t>
-  </si>
-  <si>
     <t>Conservative</t>
   </si>
   <si>
@@ -825,14 +813,31 @@
   </si>
   <si>
     <t>Liquidity stress scenario</t>
+  </si>
+  <si>
+    <t>Russell investment</t>
+  </si>
+  <si>
+    <t>iShares Aggressive</t>
+  </si>
+  <si>
+    <t>Morningstar Aggressive</t>
+  </si>
+  <si>
+    <t>Portfolio name &amp; Peer group</t>
+  </si>
+  <si>
+    <t>iShare Enhanced Conservative</t>
+  </si>
+  <si>
+    <t>To match or outperform the benchmark over a rolling three-year period</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="3">
     <numFmt numFmtId="165" formatCode="d/mm/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
@@ -1111,14 +1116,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1213,14 +1217,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,6 +1291,7 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1301,11 +1300,10 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 3" xfId="4" xr:uid="{C0DA5F93-A048-4E3B-8760-55AEF9B9D52A}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{C0DA5F93-A048-4E3B-8760-55AEF9B9D52A}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1793,7 +1791,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" spans="1:5" ht="318" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" ht="151.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2161,10 +2159,10 @@
       <c r="F6" s="27"/>
     </row>
     <row r="7" spans="2:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="77"/>
+      <c r="C7" s="76"/>
       <c r="D7" s="32" t="s">
         <v>36</v>
       </c>
@@ -2295,10 +2293,10 @@
       <c r="F18" s="27"/>
     </row>
     <row r="19" spans="2:6" ht="29" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="77"/>
+      <c r="C19" s="76"/>
       <c r="D19" s="32" t="s">
         <v>40</v>
       </c>
@@ -2311,10 +2309,18 @@
     </row>
     <row r="20" spans="2:6" ht="14.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="23"/>
+      <c r="C20" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="10">
+        <v>45458</v>
+      </c>
+      <c r="E20" s="5">
+        <v>5</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="3"/>
@@ -2340,10 +2346,10 @@
       <c r="F23" s="27"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="77"/>
+      <c r="C24" s="76"/>
       <c r="D24" s="32" t="s">
         <v>40</v>
       </c>
@@ -2389,7 +2395,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C339296D-4B2E-4C93-BBF0-FAD17EBD5E4C}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A2:AJ60"/>
+  <dimension ref="A2:AF60"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" style="33" customWidth="1"/>
@@ -2423,15 +2429,11 @@
     <col min="29" max="29" width="82.53125" style="33" customWidth="1"/>
     <col min="30" max="30" width="17.33203125" style="33" customWidth="1"/>
     <col min="31" max="32" width="9.53125" style="33" customWidth="1"/>
-    <col min="33" max="33" width="3.33203125" style="33" customWidth="1"/>
-    <col min="34" max="34" width="82.53125" style="33" customWidth="1"/>
-    <col min="35" max="35" width="17.33203125" style="33" customWidth="1"/>
-    <col min="36" max="36" width="9.53125" style="33" customWidth="1"/>
-    <col min="37" max="16384" width="8.86328125" style="33"/>
+    <col min="33" max="16384" width="8.86328125" style="33"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:36" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="3" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="2:32" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="3" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.9">
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -2460,27 +2462,23 @@
       <c r="AC3" s="35"/>
       <c r="AD3" s="35"/>
       <c r="AE3" s="35"/>
-      <c r="AF3" s="60"/>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="55"/>
-    </row>
-    <row r="4" spans="2:36" ht="14.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AF3" s="58"/>
+    </row>
+    <row r="4" spans="2:32" ht="14.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="36">
         <v>1</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="51" t="s">
         <v>46</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="E4" s="39"/>
       <c r="I4" s="36">
         <v>1</v>
       </c>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="51" t="s">
         <v>46</v>
       </c>
       <c r="K4" s="38" t="s">
@@ -2490,50 +2488,40 @@
       <c r="P4" s="36">
         <v>1</v>
       </c>
-      <c r="Q4" s="53" t="s">
+      <c r="Q4" s="51" t="s">
         <v>46</v>
       </c>
       <c r="R4" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S4" s="39"/>
       <c r="W4" s="36">
         <v>1</v>
       </c>
-      <c r="X4" s="53" t="s">
+      <c r="X4" s="51" t="s">
         <v>46</v>
       </c>
       <c r="Y4" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z4" s="39"/>
       <c r="AB4" s="36">
         <v>1</v>
       </c>
-      <c r="AC4" s="53" t="s">
+      <c r="AC4" s="51" t="s">
         <v>46</v>
       </c>
       <c r="AD4" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE4" s="39"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="36">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI4" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="AJ4" s="39"/>
-    </row>
-    <row r="5" spans="2:36" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="AF4" s="61"/>
+    </row>
+    <row r="5" spans="2:32" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B5" s="36">
-        <v>1</v>
-      </c>
-      <c r="C5" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="51" t="s">
         <v>49</v>
       </c>
       <c r="D5" s="38" t="s">
@@ -2541,9 +2529,9 @@
       </c>
       <c r="E5" s="39"/>
       <c r="I5" s="36">
-        <v>1</v>
-      </c>
-      <c r="J5" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="51" t="s">
         <v>49</v>
       </c>
       <c r="K5" s="38" t="s">
@@ -2551,9 +2539,9 @@
       </c>
       <c r="L5" s="39"/>
       <c r="P5" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="51" t="s">
         <v>49</v>
       </c>
       <c r="R5" s="38" t="s">
@@ -2561,9 +2549,9 @@
       </c>
       <c r="S5" s="39"/>
       <c r="W5" s="36">
-        <v>1</v>
-      </c>
-      <c r="X5" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="X5" s="51" t="s">
         <v>49</v>
       </c>
       <c r="Y5" s="38" t="s">
@@ -2571,32 +2559,22 @@
       </c>
       <c r="Z5" s="39"/>
       <c r="AB5" s="36">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="51" t="s">
         <v>49</v>
       </c>
       <c r="AD5" s="38" t="s">
         <v>109</v>
       </c>
       <c r="AE5" s="39"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="36">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI5" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ5" s="39"/>
-    </row>
-    <row r="6" spans="2:36" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="AF5" s="61"/>
+    </row>
+    <row r="6" spans="2:32" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B6" s="36">
-        <v>2</v>
-      </c>
-      <c r="C6" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="51" t="s">
         <v>50</v>
       </c>
       <c r="D6" s="38" t="s">
@@ -2604,9 +2582,9 @@
       </c>
       <c r="E6" s="39"/>
       <c r="I6" s="36">
-        <v>2</v>
-      </c>
-      <c r="J6" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="51" t="s">
         <v>50</v>
       </c>
       <c r="K6" s="38" t="s">
@@ -2614,9 +2592,9 @@
       </c>
       <c r="L6" s="39"/>
       <c r="P6" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="51" t="s">
         <v>50</v>
       </c>
       <c r="R6" s="38" t="s">
@@ -2624,9 +2602,9 @@
       </c>
       <c r="S6" s="39"/>
       <c r="W6" s="36">
-        <v>2</v>
-      </c>
-      <c r="X6" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="X6" s="51" t="s">
         <v>50</v>
       </c>
       <c r="Y6" s="38" t="s">
@@ -2634,473 +2612,393 @@
       </c>
       <c r="Z6" s="39"/>
       <c r="AB6" s="36">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC6" s="51" t="s">
         <v>50</v>
       </c>
       <c r="AD6" s="38" t="s">
         <v>110</v>
       </c>
       <c r="AE6" s="39"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="36">
-        <v>2</v>
-      </c>
-      <c r="AH6" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI6" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ6" s="39"/>
-    </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B7" s="40">
-        <v>3</v>
-      </c>
-      <c r="C7" s="53" t="s">
+      <c r="AF6" s="61"/>
+    </row>
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B7" s="36">
+        <v>4</v>
+      </c>
+      <c r="C7" s="51" t="s">
         <v>51</v>
       </c>
       <c r="D7" s="38">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="I7" s="40">
-        <v>3</v>
-      </c>
-      <c r="J7" s="53" t="s">
+      <c r="E7" s="40"/>
+      <c r="I7" s="36">
+        <v>4</v>
+      </c>
+      <c r="J7" s="51" t="s">
         <v>51</v>
       </c>
       <c r="K7" s="38">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="L7" s="41"/>
-      <c r="P7" s="40">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="53" t="s">
+      <c r="L7" s="40"/>
+      <c r="P7" s="36">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="51" t="s">
         <v>51</v>
       </c>
       <c r="R7" s="38">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="S7" s="41"/>
-      <c r="W7" s="40">
-        <v>3</v>
-      </c>
-      <c r="X7" s="53" t="s">
+      <c r="S7" s="40"/>
+      <c r="W7" s="36">
+        <v>4</v>
+      </c>
+      <c r="X7" s="51" t="s">
         <v>51</v>
       </c>
       <c r="Y7" s="38">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="Z7" s="41"/>
-      <c r="AB7" s="40">
-        <v>3</v>
-      </c>
-      <c r="AC7" s="53" t="s">
+      <c r="Z7" s="40"/>
+      <c r="AB7" s="36">
+        <v>4</v>
+      </c>
+      <c r="AC7" s="51" t="s">
         <v>51</v>
       </c>
       <c r="AD7" s="38">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="64"/>
-      <c r="AG7" s="40">
-        <v>3</v>
-      </c>
-      <c r="AH7" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI7" s="38">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="AJ7" s="41"/>
-    </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B8" s="40">
-        <v>4</v>
-      </c>
-      <c r="C8" s="53" t="s">
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="62"/>
+    </row>
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B8" s="36">
+        <v>5</v>
+      </c>
+      <c r="C8" s="51" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="38">
         <v>0.18</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="I8" s="40">
-        <v>4</v>
-      </c>
-      <c r="J8" s="53" t="s">
+      <c r="E8" s="40"/>
+      <c r="I8" s="36">
+        <v>5</v>
+      </c>
+      <c r="J8" s="51" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="38">
         <v>0.18</v>
       </c>
-      <c r="L8" s="41"/>
-      <c r="P8" s="40">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="53" t="s">
+      <c r="L8" s="40"/>
+      <c r="P8" s="36">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="51" t="s">
         <v>52</v>
       </c>
       <c r="R8" s="38">
         <v>0.18</v>
       </c>
-      <c r="S8" s="41"/>
-      <c r="W8" s="40">
-        <v>4</v>
-      </c>
-      <c r="X8" s="53" t="s">
+      <c r="S8" s="40"/>
+      <c r="W8" s="36">
+        <v>5</v>
+      </c>
+      <c r="X8" s="51" t="s">
         <v>52</v>
       </c>
       <c r="Y8" s="38">
         <v>0.18</v>
       </c>
-      <c r="Z8" s="41"/>
-      <c r="AB8" s="40">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="53" t="s">
+      <c r="Z8" s="40"/>
+      <c r="AB8" s="36">
+        <v>5</v>
+      </c>
+      <c r="AC8" s="51" t="s">
         <v>52</v>
       </c>
       <c r="AD8" s="38">
         <v>0.18</v>
       </c>
-      <c r="AE8" s="41"/>
-      <c r="AF8" s="64"/>
-      <c r="AG8" s="40">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI8" s="38">
-        <v>0.18</v>
-      </c>
-      <c r="AJ8" s="41"/>
-    </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B9" s="40">
-        <v>5</v>
-      </c>
-      <c r="C9" s="53" t="s">
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="62"/>
+    </row>
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B9" s="36">
+        <v>6</v>
+      </c>
+      <c r="C9" s="51" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="38">
         <v>0.01</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="I9" s="40">
-        <v>5</v>
-      </c>
-      <c r="J9" s="53" t="s">
+      <c r="E9" s="40"/>
+      <c r="I9" s="36">
+        <v>6</v>
+      </c>
+      <c r="J9" s="51" t="s">
         <v>53</v>
       </c>
       <c r="K9" s="38">
         <v>0.01</v>
       </c>
-      <c r="L9" s="41"/>
-      <c r="P9" s="40">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="53" t="s">
+      <c r="L9" s="40"/>
+      <c r="P9" s="36">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="51" t="s">
         <v>53</v>
       </c>
       <c r="R9" s="38">
         <v>0.01</v>
       </c>
-      <c r="S9" s="41"/>
-      <c r="W9" s="40">
-        <v>5</v>
-      </c>
-      <c r="X9" s="53" t="s">
+      <c r="S9" s="40"/>
+      <c r="W9" s="36">
+        <v>6</v>
+      </c>
+      <c r="X9" s="51" t="s">
         <v>53</v>
       </c>
       <c r="Y9" s="38">
         <v>0.01</v>
       </c>
-      <c r="Z9" s="41"/>
-      <c r="AB9" s="40">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="53" t="s">
+      <c r="Z9" s="40"/>
+      <c r="AB9" s="36">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="51" t="s">
         <v>53</v>
       </c>
       <c r="AD9" s="38">
         <v>0.01</v>
       </c>
-      <c r="AE9" s="41"/>
-      <c r="AF9" s="64"/>
-      <c r="AG9" s="40">
-        <v>5</v>
-      </c>
-      <c r="AH9" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI9" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="AJ9" s="41"/>
-    </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B10" s="40">
-        <v>6</v>
-      </c>
-      <c r="C10" s="53" t="s">
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="62"/>
+    </row>
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B10" s="36">
+        <v>7</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>54</v>
       </c>
       <c r="D10" s="38" t="s">
         <v>111</v>
       </c>
       <c r="E10" s="39"/>
-      <c r="I10" s="40">
-        <v>6</v>
-      </c>
-      <c r="J10" s="53" t="s">
+      <c r="I10" s="36">
+        <v>7</v>
+      </c>
+      <c r="J10" s="51" t="s">
         <v>54</v>
       </c>
       <c r="K10" s="38" t="s">
         <v>111</v>
       </c>
       <c r="L10" s="39"/>
-      <c r="P10" s="40">
-        <v>6</v>
-      </c>
-      <c r="Q10" s="53" t="s">
+      <c r="P10" s="36">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="51" t="s">
         <v>54</v>
       </c>
       <c r="R10" s="38" t="s">
         <v>111</v>
       </c>
       <c r="S10" s="39"/>
-      <c r="W10" s="40">
-        <v>6</v>
-      </c>
-      <c r="X10" s="53" t="s">
+      <c r="W10" s="36">
+        <v>7</v>
+      </c>
+      <c r="X10" s="51" t="s">
         <v>54</v>
       </c>
       <c r="Y10" s="38" t="s">
         <v>111</v>
       </c>
       <c r="Z10" s="39"/>
-      <c r="AB10" s="40">
-        <v>6</v>
-      </c>
-      <c r="AC10" s="53" t="s">
+      <c r="AB10" s="36">
+        <v>7</v>
+      </c>
+      <c r="AC10" s="51" t="s">
         <v>54</v>
       </c>
       <c r="AD10" s="38" t="s">
         <v>111</v>
       </c>
       <c r="AE10" s="39"/>
-      <c r="AF10" s="63"/>
-      <c r="AG10" s="40">
-        <v>6</v>
-      </c>
-      <c r="AH10" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI10" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="AJ10" s="39"/>
-    </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B11" s="40">
-        <v>7</v>
-      </c>
-      <c r="C11" s="53" t="s">
+      <c r="AF10" s="61"/>
+    </row>
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B11" s="36">
+        <v>8</v>
+      </c>
+      <c r="C11" s="51" t="s">
         <v>55</v>
       </c>
       <c r="D11" s="38" t="s">
         <v>56</v>
       </c>
       <c r="E11" s="39"/>
-      <c r="I11" s="40">
-        <v>7</v>
-      </c>
-      <c r="J11" s="53" t="s">
+      <c r="I11" s="36">
+        <v>8</v>
+      </c>
+      <c r="J11" s="51" t="s">
         <v>55</v>
       </c>
       <c r="K11" s="38" t="s">
         <v>56</v>
       </c>
       <c r="L11" s="39"/>
-      <c r="P11" s="40">
-        <v>7</v>
-      </c>
-      <c r="Q11" s="53" t="s">
+      <c r="P11" s="36">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="51" t="s">
         <v>55</v>
       </c>
       <c r="R11" s="38" t="s">
         <v>56</v>
       </c>
       <c r="S11" s="39"/>
-      <c r="W11" s="40">
-        <v>7</v>
-      </c>
-      <c r="X11" s="53" t="s">
+      <c r="W11" s="36">
+        <v>8</v>
+      </c>
+      <c r="X11" s="51" t="s">
         <v>55</v>
       </c>
       <c r="Y11" s="38" t="s">
         <v>56</v>
       </c>
       <c r="Z11" s="39"/>
-      <c r="AB11" s="40">
-        <v>7</v>
-      </c>
-      <c r="AC11" s="53" t="s">
+      <c r="AB11" s="36">
+        <v>8</v>
+      </c>
+      <c r="AC11" s="51" t="s">
         <v>55</v>
       </c>
       <c r="AD11" s="38" t="s">
         <v>56</v>
       </c>
       <c r="AE11" s="39"/>
-      <c r="AF11" s="63"/>
-      <c r="AG11" s="40">
-        <v>7</v>
-      </c>
-      <c r="AH11" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI11" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="AJ11" s="39"/>
-    </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B12" s="40">
-        <v>8</v>
-      </c>
-      <c r="C12" s="53" t="s">
+      <c r="AF11" s="61"/>
+    </row>
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B12" s="36">
+        <v>9</v>
+      </c>
+      <c r="C12" s="51" t="s">
         <v>57</v>
       </c>
       <c r="D12" s="38">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="I12" s="40">
-        <v>8</v>
-      </c>
-      <c r="J12" s="53" t="s">
+      <c r="E12" s="40"/>
+      <c r="I12" s="36">
+        <v>9</v>
+      </c>
+      <c r="J12" s="51" t="s">
         <v>57</v>
       </c>
       <c r="K12" s="38">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="L12" s="41"/>
-      <c r="P12" s="40">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="53" t="s">
+      <c r="L12" s="40"/>
+      <c r="P12" s="36">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="51" t="s">
         <v>57</v>
       </c>
       <c r="R12" s="38">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="S12" s="41"/>
-      <c r="W12" s="40">
-        <v>8</v>
-      </c>
-      <c r="X12" s="53" t="s">
+      <c r="S12" s="40"/>
+      <c r="W12" s="36">
+        <v>9</v>
+      </c>
+      <c r="X12" s="51" t="s">
         <v>57</v>
       </c>
       <c r="Y12" s="38">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Z12" s="41"/>
-      <c r="AB12" s="40">
-        <v>8</v>
-      </c>
-      <c r="AC12" s="53" t="s">
+      <c r="Z12" s="40"/>
+      <c r="AB12" s="36">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="51" t="s">
         <v>57</v>
       </c>
       <c r="AD12" s="38">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AE12" s="41"/>
-      <c r="AF12" s="64"/>
-      <c r="AG12" s="40">
-        <v>8</v>
-      </c>
-      <c r="AH12" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI12" s="38">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="AJ12" s="41"/>
-    </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B13" s="40">
-        <v>9</v>
-      </c>
-      <c r="C13" s="53" t="s">
+      <c r="AE12" s="40"/>
+      <c r="AF12" s="62"/>
+    </row>
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B13" s="36">
+        <v>10</v>
+      </c>
+      <c r="C13" s="51" t="s">
         <v>58</v>
       </c>
       <c r="D13" s="38" t="s">
         <v>59</v>
       </c>
       <c r="E13" s="39"/>
-      <c r="I13" s="40">
-        <v>9</v>
-      </c>
-      <c r="J13" s="53" t="s">
+      <c r="I13" s="36">
+        <v>10</v>
+      </c>
+      <c r="J13" s="51" t="s">
         <v>58</v>
       </c>
       <c r="K13" s="38" t="s">
         <v>59</v>
       </c>
       <c r="L13" s="39"/>
-      <c r="P13" s="40">
-        <v>9</v>
-      </c>
-      <c r="Q13" s="53" t="s">
+      <c r="P13" s="36">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="51" t="s">
         <v>58</v>
       </c>
       <c r="R13" s="38" t="s">
         <v>59</v>
       </c>
       <c r="S13" s="39"/>
-      <c r="W13" s="40">
-        <v>9</v>
-      </c>
-      <c r="X13" s="53" t="s">
+      <c r="W13" s="36">
+        <v>10</v>
+      </c>
+      <c r="X13" s="51" t="s">
         <v>58</v>
       </c>
       <c r="Y13" s="38" t="s">
         <v>59</v>
       </c>
       <c r="Z13" s="39"/>
-      <c r="AB13" s="40">
-        <v>9</v>
-      </c>
-      <c r="AC13" s="53" t="s">
+      <c r="AB13" s="36">
+        <v>10</v>
+      </c>
+      <c r="AC13" s="51" t="s">
         <v>58</v>
       </c>
       <c r="AD13" s="38" t="s">
         <v>59</v>
       </c>
       <c r="AE13" s="39"/>
-      <c r="AF13" s="63"/>
-      <c r="AG13" s="40">
-        <v>9</v>
-      </c>
-      <c r="AH13" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI13" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ13" s="39"/>
-    </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+      <c r="AF13" s="61"/>
+    </row>
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" s="36">
-        <v>1</v>
-      </c>
-      <c r="C14" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="51" t="s">
         <v>60</v>
       </c>
       <c r="D14" s="38" t="s">
@@ -3108,9 +3006,9 @@
       </c>
       <c r="E14" s="39"/>
       <c r="I14" s="36">
-        <v>1</v>
-      </c>
-      <c r="J14" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="51" t="s">
         <v>60</v>
       </c>
       <c r="K14" s="38" t="s">
@@ -3118,9 +3016,9 @@
       </c>
       <c r="L14" s="39"/>
       <c r="P14" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="51" t="s">
         <v>60</v>
       </c>
       <c r="R14" s="38" t="s">
@@ -3128,9 +3026,9 @@
       </c>
       <c r="S14" s="39"/>
       <c r="W14" s="36">
-        <v>1</v>
-      </c>
-      <c r="X14" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="X14" s="51" t="s">
         <v>60</v>
       </c>
       <c r="Y14" s="38" t="s">
@@ -3138,32 +3036,22 @@
       </c>
       <c r="Z14" s="39"/>
       <c r="AB14" s="36">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC14" s="51" t="s">
         <v>60</v>
       </c>
       <c r="AD14" s="38" t="s">
         <v>112</v>
       </c>
       <c r="AE14" s="39"/>
-      <c r="AF14" s="63"/>
-      <c r="AG14" s="36">
-        <v>1</v>
-      </c>
-      <c r="AH14" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI14" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="AJ14" s="39"/>
-    </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+      <c r="AF14" s="61"/>
+    </row>
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" s="36">
-        <v>2</v>
-      </c>
-      <c r="C15" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="51" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="38" t="s">
@@ -3171,9 +3059,9 @@
       </c>
       <c r="E15" s="39"/>
       <c r="I15" s="36">
-        <v>2</v>
-      </c>
-      <c r="J15" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="51" t="s">
         <v>61</v>
       </c>
       <c r="K15" s="38" t="s">
@@ -3181,9 +3069,9 @@
       </c>
       <c r="L15" s="39"/>
       <c r="P15" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="51" t="s">
         <v>61</v>
       </c>
       <c r="R15" s="38" t="s">
@@ -3191,9 +3079,9 @@
       </c>
       <c r="S15" s="39"/>
       <c r="W15" s="36">
-        <v>2</v>
-      </c>
-      <c r="X15" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="X15" s="51" t="s">
         <v>61</v>
       </c>
       <c r="Y15" s="38" t="s">
@@ -3201,32 +3089,22 @@
       </c>
       <c r="Z15" s="39"/>
       <c r="AB15" s="36">
-        <v>2</v>
-      </c>
-      <c r="AC15" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC15" s="51" t="s">
         <v>61</v>
       </c>
       <c r="AD15" s="38" t="s">
         <v>113</v>
       </c>
       <c r="AE15" s="39"/>
-      <c r="AF15" s="63"/>
-      <c r="AG15" s="36">
-        <v>2</v>
-      </c>
-      <c r="AH15" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI15" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ15" s="39"/>
-    </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+      <c r="AF15" s="61"/>
+    </row>
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" s="36">
-        <v>3</v>
-      </c>
-      <c r="C16" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="51" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="38" t="s">
@@ -3234,9 +3112,9 @@
       </c>
       <c r="E16" s="39"/>
       <c r="I16" s="36">
-        <v>3</v>
-      </c>
-      <c r="J16" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="51" t="s">
         <v>62</v>
       </c>
       <c r="K16" s="38" t="s">
@@ -3244,9 +3122,9 @@
       </c>
       <c r="L16" s="39"/>
       <c r="P16" s="36">
-        <v>3</v>
-      </c>
-      <c r="Q16" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="51" t="s">
         <v>62</v>
       </c>
       <c r="R16" s="38" t="s">
@@ -3254,9 +3132,9 @@
       </c>
       <c r="S16" s="39"/>
       <c r="W16" s="36">
-        <v>3</v>
-      </c>
-      <c r="X16" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="X16" s="51" t="s">
         <v>62</v>
       </c>
       <c r="Y16" s="38" t="s">
@@ -3264,32 +3142,22 @@
       </c>
       <c r="Z16" s="39"/>
       <c r="AB16" s="36">
-        <v>3</v>
-      </c>
-      <c r="AC16" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC16" s="51" t="s">
         <v>62</v>
       </c>
       <c r="AD16" s="38" t="s">
         <v>114</v>
       </c>
       <c r="AE16" s="39"/>
-      <c r="AF16" s="63"/>
-      <c r="AG16" s="36">
-        <v>3</v>
-      </c>
-      <c r="AH16" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI16" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="AJ16" s="39"/>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="AF16" s="61"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
       <c r="B17" s="36">
-        <v>4</v>
-      </c>
-      <c r="C17" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="51" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="38" t="s">
@@ -3297,9 +3165,9 @@
       </c>
       <c r="E17" s="39"/>
       <c r="I17" s="36">
-        <v>4</v>
-      </c>
-      <c r="J17" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="51" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="38" t="s">
@@ -3307,9 +3175,9 @@
       </c>
       <c r="L17" s="39"/>
       <c r="P17" s="36">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="51" t="s">
         <v>63</v>
       </c>
       <c r="R17" s="38" t="s">
@@ -3317,9 +3185,9 @@
       </c>
       <c r="S17" s="39"/>
       <c r="W17" s="36">
-        <v>4</v>
-      </c>
-      <c r="X17" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="X17" s="51" t="s">
         <v>63</v>
       </c>
       <c r="Y17" s="38" t="s">
@@ -3327,1535 +3195,1352 @@
       </c>
       <c r="Z17" s="39"/>
       <c r="AB17" s="36">
-        <v>4</v>
-      </c>
-      <c r="AC17" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC17" s="51" t="s">
         <v>63</v>
       </c>
       <c r="AD17" s="38" t="s">
         <v>115</v>
       </c>
       <c r="AE17" s="39"/>
-      <c r="AF17" s="63"/>
-      <c r="AG17" s="36">
-        <v>4</v>
-      </c>
-      <c r="AH17" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI17" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ17" s="39"/>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B18" s="42">
-        <v>5</v>
-      </c>
-      <c r="C18" s="53" t="s">
+      <c r="AF17" s="61"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B18" s="36">
+        <v>15</v>
+      </c>
+      <c r="C18" s="51" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="38" t="s">
         <v>116</v>
       </c>
       <c r="E18" s="39"/>
-      <c r="I18" s="42">
-        <v>5</v>
-      </c>
-      <c r="J18" s="53" t="s">
+      <c r="I18" s="36">
+        <v>15</v>
+      </c>
+      <c r="J18" s="51" t="s">
         <v>64</v>
       </c>
       <c r="K18" s="38" t="s">
         <v>116</v>
       </c>
       <c r="L18" s="39"/>
-      <c r="P18" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="53" t="s">
+      <c r="P18" s="36">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="51" t="s">
         <v>64</v>
       </c>
       <c r="R18" s="38" t="s">
         <v>116</v>
       </c>
       <c r="S18" s="39"/>
-      <c r="W18" s="42">
-        <v>5</v>
-      </c>
-      <c r="X18" s="53" t="s">
+      <c r="W18" s="36">
+        <v>15</v>
+      </c>
+      <c r="X18" s="51" t="s">
         <v>64</v>
       </c>
       <c r="Y18" s="38" t="s">
         <v>116</v>
       </c>
       <c r="Z18" s="39"/>
-      <c r="AB18" s="42">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="53" t="s">
+      <c r="AB18" s="36">
+        <v>15</v>
+      </c>
+      <c r="AC18" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="AD18" s="38" t="s">
-        <v>116</v>
-      </c>
+      <c r="AD18" s="38"/>
       <c r="AE18" s="39"/>
-      <c r="AF18" s="63"/>
-      <c r="AG18" s="42">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI18" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="AJ18" s="39"/>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A19" s="52"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="73" t="s">
-        <v>218</v>
+      <c r="AF18" s="61"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A19" s="50"/>
+      <c r="B19" s="36">
+        <v>16</v>
+      </c>
+      <c r="C19" s="71" t="s">
+        <v>216</v>
       </c>
       <c r="D19" t="s">
+        <v>224</v>
+      </c>
+      <c r="I19" s="36">
+        <v>16</v>
+      </c>
+      <c r="J19" s="71" t="s">
+        <v>216</v>
+      </c>
+      <c r="K19" t="s">
+        <v>227</v>
+      </c>
+      <c r="P19" s="36">
+        <v>16</v>
+      </c>
+      <c r="Q19" s="71" t="s">
+        <v>216</v>
+      </c>
+      <c r="R19" t="s">
+        <v>223</v>
+      </c>
+      <c r="W19" s="36">
+        <v>16</v>
+      </c>
+      <c r="X19" s="71" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y19" t="s">
         <v>226</v>
       </c>
-      <c r="I19" s="52"/>
-      <c r="J19" s="73" t="s">
-        <v>218</v>
-      </c>
-      <c r="K19" t="s">
-        <v>229</v>
-      </c>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="73" t="s">
-        <v>218</v>
-      </c>
-      <c r="R19" t="s">
-        <v>225</v>
-      </c>
-      <c r="W19" s="52"/>
-      <c r="X19" s="73" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AB19" s="52"/>
-      <c r="AC19" s="73" t="s">
-        <v>218</v>
+      <c r="AB19" s="36">
+        <v>16</v>
+      </c>
+      <c r="AC19" s="71" t="s">
+        <v>216</v>
       </c>
       <c r="AD19" t="s">
-        <v>223</v>
-      </c>
-      <c r="AG19" s="52"/>
-      <c r="AH19" s="73" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A20" s="52"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="73" t="s">
-        <v>137</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A20" s="50"/>
+      <c r="B20" s="36">
+        <v>17</v>
+      </c>
+      <c r="C20" s="71" t="s">
+        <v>135</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
-      <c r="I20" s="52"/>
-      <c r="J20" s="73" t="s">
-        <v>137</v>
+      <c r="I20" s="36">
+        <v>17</v>
+      </c>
+      <c r="J20" s="71" t="s">
+        <v>135</v>
       </c>
       <c r="K20" t="s">
         <v>48</v>
       </c>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="73" t="s">
-        <v>137</v>
+      <c r="P20" s="36">
+        <v>17</v>
+      </c>
+      <c r="Q20" s="71" t="s">
+        <v>135</v>
       </c>
       <c r="R20" t="s">
         <v>48</v>
       </c>
-      <c r="W20" s="52"/>
-      <c r="X20" s="73" t="s">
-        <v>137</v>
+      <c r="W20" s="36">
+        <v>17</v>
+      </c>
+      <c r="X20" s="71" t="s">
+        <v>135</v>
       </c>
       <c r="Y20" t="s">
         <v>48</v>
       </c>
-      <c r="AB20" s="52"/>
-      <c r="AC20" s="73" t="s">
-        <v>137</v>
+      <c r="AB20" s="36">
+        <v>17</v>
+      </c>
+      <c r="AC20" s="71" t="s">
+        <v>135</v>
       </c>
       <c r="AD20" t="s">
         <v>48</v>
       </c>
-      <c r="AG20" s="52"/>
-      <c r="AH20" s="73" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A21" s="52"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="73" t="s">
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A21" s="50"/>
+      <c r="B21" s="36">
+        <v>18</v>
+      </c>
+      <c r="C21" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="D21" t="s">
+        <v>225</v>
+      </c>
+      <c r="I21" s="36">
+        <v>18</v>
+      </c>
+      <c r="J21" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="K21" t="s">
+        <v>222</v>
+      </c>
+      <c r="P21" s="36">
+        <v>18</v>
+      </c>
+      <c r="Q21" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="R21" t="s">
+        <v>222</v>
+      </c>
+      <c r="W21" s="36">
+        <v>18</v>
+      </c>
+      <c r="X21" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>222</v>
+      </c>
+      <c r="AB21" s="36">
+        <v>18</v>
+      </c>
+      <c r="AC21" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A22" s="50"/>
+      <c r="B22" s="36">
+        <v>19</v>
+      </c>
+      <c r="C22" s="71" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" t="s">
+        <v>228</v>
+      </c>
+      <c r="I22" s="36">
+        <v>19</v>
+      </c>
+      <c r="J22" s="71" t="s">
+        <v>218</v>
+      </c>
+      <c r="K22" t="s">
+        <v>228</v>
+      </c>
+      <c r="P22" s="36">
+        <v>19</v>
+      </c>
+      <c r="Q22" s="71" t="s">
+        <v>218</v>
+      </c>
+      <c r="R22" t="s">
+        <v>228</v>
+      </c>
+      <c r="W22" s="36">
+        <v>19</v>
+      </c>
+      <c r="X22" s="71" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>228</v>
+      </c>
+      <c r="AB22" s="36">
+        <v>19</v>
+      </c>
+      <c r="AC22" s="71" t="s">
+        <v>218</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A23" s="50"/>
+      <c r="B23" s="36">
+        <v>20</v>
+      </c>
+      <c r="C23" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="D21" t="s">
-        <v>227</v>
-      </c>
-      <c r="I21" s="52"/>
-      <c r="J21" s="73" t="s">
+      <c r="D23" t="s">
+        <v>231</v>
+      </c>
+      <c r="I23" s="36">
+        <v>20</v>
+      </c>
+      <c r="J23" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="K21" t="s">
-        <v>224</v>
-      </c>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="73" t="s">
+      <c r="K23" t="s">
+        <v>230</v>
+      </c>
+      <c r="P23" s="36">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="R21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W21" s="52"/>
-      <c r="X21" s="73" t="s">
+      <c r="R23" t="s">
+        <v>230</v>
+      </c>
+      <c r="W23" s="36">
+        <v>20</v>
+      </c>
+      <c r="X23" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="Y21" t="s">
-        <v>224</v>
-      </c>
-      <c r="AB21" s="52"/>
-      <c r="AC21" s="73" t="s">
+      <c r="Y23" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB23" s="36">
+        <v>20</v>
+      </c>
+      <c r="AC23" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="AD21" t="s">
-        <v>224</v>
-      </c>
-      <c r="AG21" s="52"/>
-      <c r="AH21" s="73" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A22" s="52"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="73" t="s">
+      <c r="AD23" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A24" s="50"/>
+      <c r="B24" s="36">
+        <v>21</v>
+      </c>
+      <c r="C24" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="D22" t="s">
-        <v>230</v>
-      </c>
-      <c r="I22" s="52"/>
-      <c r="J22" s="73" t="s">
+      <c r="D24" t="s">
+        <v>264</v>
+      </c>
+      <c r="I24" s="36">
+        <v>21</v>
+      </c>
+      <c r="J24" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="K22" t="s">
-        <v>230</v>
-      </c>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="73" t="s">
+      <c r="K24" t="s">
+        <v>233</v>
+      </c>
+      <c r="P24" s="36">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="R22" t="s">
-        <v>230</v>
-      </c>
-      <c r="W22" s="52"/>
-      <c r="X22" s="73" t="s">
+      <c r="R24" t="s">
+        <v>233</v>
+      </c>
+      <c r="W24" s="36">
+        <v>21</v>
+      </c>
+      <c r="X24" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="Y22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AB22" s="52"/>
-      <c r="AC22" s="73" t="s">
+      <c r="Y24" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB24" s="36">
+        <v>21</v>
+      </c>
+      <c r="AC24" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="AD22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AG22" s="52"/>
-      <c r="AH22" s="73" t="s">
-        <v>220</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A23" s="52"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="73" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="AD24" t="s">
         <v>233</v>
       </c>
-      <c r="I23" s="52"/>
-      <c r="J23" s="73" t="s">
-        <v>221</v>
-      </c>
-      <c r="K23" t="s">
-        <v>232</v>
-      </c>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="73" t="s">
-        <v>221</v>
-      </c>
-      <c r="R23" t="s">
-        <v>232</v>
-      </c>
-      <c r="W23" s="52"/>
-      <c r="X23" s="73" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>234</v>
-      </c>
-      <c r="AB23" s="52"/>
-      <c r="AC23" s="73" t="s">
-        <v>221</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>231</v>
-      </c>
-      <c r="AG23" s="52"/>
-      <c r="AH23" s="73" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A24" s="52"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="D24" t="s">
-        <v>235</v>
-      </c>
-      <c r="I24" s="52"/>
-      <c r="J24" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="K24" t="s">
-        <v>235</v>
-      </c>
-      <c r="P24" s="52"/>
-      <c r="Q24" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="R24" t="s">
-        <v>235</v>
-      </c>
-      <c r="W24" s="52"/>
-      <c r="X24" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>235</v>
-      </c>
-      <c r="AB24" s="52"/>
-      <c r="AC24" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>235</v>
-      </c>
-      <c r="AG24" s="52"/>
-      <c r="AH24" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="25" spans="1:36" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="25" spans="1:32" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="F25" s="33"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-    </row>
-    <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+    </row>
+    <row r="26" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.9">
       <c r="B26" s="35"/>
       <c r="C26" s="35"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="35"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="55"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="61"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="60"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="59"/>
+      <c r="R26" s="58"/>
+      <c r="S26" s="58"/>
       <c r="W26" s="35"/>
       <c r="X26" s="37"/>
       <c r="Y26" s="35"/>
       <c r="Z26" s="35"/>
-      <c r="AB26" s="55"/>
-      <c r="AC26" s="53"/>
-      <c r="AD26" s="55"/>
-      <c r="AE26" s="55"/>
-      <c r="AF26" s="60"/>
-      <c r="AG26" s="55"/>
-      <c r="AH26" s="53"/>
-      <c r="AI26" s="55"/>
-      <c r="AJ26" s="55"/>
-    </row>
-    <row r="27" spans="1:36" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="43"/>
-      <c r="C27" s="54" t="s">
+      <c r="AB26" s="53"/>
+      <c r="AC26" s="51"/>
+      <c r="AD26" s="53"/>
+      <c r="AE26" s="53"/>
+      <c r="AF26" s="58"/>
+    </row>
+    <row r="27" spans="1:32" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B27" s="41"/>
+      <c r="C27" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="54" t="s">
+      <c r="D27" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="54" t="s">
+      <c r="E27" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="I27" s="44"/>
-      <c r="J27" s="54" t="s">
+      <c r="I27" s="42"/>
+      <c r="J27" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="K27" s="45" t="s">
+      <c r="K27" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="L27" s="45" t="s">
+      <c r="L27" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="54" t="s">
+      <c r="P27" s="42"/>
+      <c r="Q27" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="R27" s="45" t="s">
+      <c r="R27" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="S27" s="45" t="s">
+      <c r="S27" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="W27" s="44"/>
-      <c r="X27" s="54" t="s">
+      <c r="W27" s="42"/>
+      <c r="X27" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="Y27" s="45" t="s">
+      <c r="Y27" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="Z27" s="45" t="s">
+      <c r="Z27" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="AB27" s="44"/>
-      <c r="AC27" s="54" t="s">
+      <c r="AB27" s="42"/>
+      <c r="AC27" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="AD27" s="45" t="s">
+      <c r="AD27" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="AE27" s="45" t="s">
+      <c r="AE27" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="AF27" s="65"/>
-      <c r="AG27" s="44"/>
-      <c r="AH27" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI27" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ27" s="45" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:36" ht="14.75" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="B28" s="55"/>
-      <c r="C28" s="54" t="s">
+      <c r="AF27" s="63"/>
+    </row>
+    <row r="28" spans="1:32" ht="14.75" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B28" s="53"/>
+      <c r="C28" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
       <c r="F28" s="35"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="53" t="s">
+      <c r="I28" s="53"/>
+      <c r="J28" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="K28" s="55"/>
-      <c r="L28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="53" t="s">
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="R28" s="55"/>
-      <c r="S28" s="55"/>
-      <c r="W28" s="55"/>
-      <c r="X28" s="53" t="s">
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="W28" s="53"/>
+      <c r="X28" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="Y28" s="55"/>
-      <c r="Z28" s="55"/>
-      <c r="AB28" s="55"/>
-      <c r="AC28" s="53" t="s">
+      <c r="Y28" s="53"/>
+      <c r="Z28" s="53"/>
+      <c r="AB28" s="53"/>
+      <c r="AC28" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="AD28" s="55"/>
-      <c r="AE28" s="55"/>
-      <c r="AF28" s="60"/>
-      <c r="AG28" s="55"/>
-      <c r="AH28" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI28" s="55"/>
-      <c r="AJ28" s="55"/>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B29" s="43"/>
-      <c r="C29" s="53" t="s">
+      <c r="AD28" s="53"/>
+      <c r="AE28" s="53"/>
+      <c r="AF28" s="58"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B29" s="41"/>
+      <c r="C29" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="56">
+      <c r="D29" s="54">
         <v>0</v>
       </c>
-      <c r="E29" s="56">
+      <c r="E29" s="54">
         <v>0.4</v>
       </c>
-      <c r="I29" s="43"/>
-      <c r="J29" s="53" t="s">
+      <c r="I29" s="41"/>
+      <c r="J29" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="K29" s="58">
+      <c r="K29" s="56">
+        <v>0.05</v>
+      </c>
+      <c r="L29" s="56">
+        <v>0.45</v>
+      </c>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="R29" s="56">
+        <v>0.05</v>
+      </c>
+      <c r="S29" s="56">
+        <v>0.45</v>
+      </c>
+      <c r="W29" s="41"/>
+      <c r="X29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y29" s="56">
+        <v>0.04</v>
+      </c>
+      <c r="Z29" s="56">
+        <v>0.44</v>
+      </c>
+      <c r="AB29" s="41"/>
+      <c r="AC29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD29" s="56">
+        <v>0.09</v>
+      </c>
+      <c r="AE29" s="56">
+        <v>0.49</v>
+      </c>
+      <c r="AF29" s="64"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B30" s="41"/>
+      <c r="C30" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="54">
+        <v>0</v>
+      </c>
+      <c r="E30" s="54">
+        <v>0.45</v>
+      </c>
+      <c r="I30" s="41"/>
+      <c r="J30" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="K30" s="56">
+        <v>0.05</v>
+      </c>
+      <c r="L30" s="56">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="R30" s="56">
+        <v>0.05</v>
+      </c>
+      <c r="S30" s="56">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W30" s="41"/>
+      <c r="X30" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y30" s="56">
+        <v>0.27</v>
+      </c>
+      <c r="Z30" s="56">
+        <v>0.67</v>
+      </c>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD30" s="56">
+        <v>0.36</v>
+      </c>
+      <c r="AE30" s="56">
+        <v>0.76</v>
+      </c>
+      <c r="AF30" s="64"/>
+    </row>
+    <row r="31" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="41"/>
+      <c r="C31" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="54">
+        <v>0</v>
+      </c>
+      <c r="E31" s="54">
+        <v>0.12</v>
+      </c>
+      <c r="I31" s="41"/>
+      <c r="J31" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="K31" s="56">
+        <v>0</v>
+      </c>
+      <c r="L31" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="R31" s="56">
+        <v>0</v>
+      </c>
+      <c r="S31" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="W31" s="41"/>
+      <c r="X31" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y31" s="56">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="56">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AB31" s="41"/>
+      <c r="AC31" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD31" s="56">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="AF31" s="64"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B32" s="41"/>
+      <c r="C32" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="54">
+        <v>0</v>
+      </c>
+      <c r="E32" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="I32" s="41"/>
+      <c r="J32" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="K32" s="56">
+        <v>0</v>
+      </c>
+      <c r="L32" s="56">
+        <v>0.08</v>
+      </c>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="R32" s="56">
+        <v>0</v>
+      </c>
+      <c r="S32" s="56">
+        <v>0.08</v>
+      </c>
+      <c r="W32" s="41"/>
+      <c r="X32" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y32" s="56">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="56">
+        <v>0.08</v>
+      </c>
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD32" s="56">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="AF32" s="64"/>
+    </row>
+    <row r="33" spans="1:32" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B33" s="41"/>
+      <c r="C33" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="54">
+        <v>0</v>
+      </c>
+      <c r="E33" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="I33" s="41"/>
+      <c r="J33" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="K33" s="56">
+        <v>0</v>
+      </c>
+      <c r="L33" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="R33" s="56">
+        <v>0</v>
+      </c>
+      <c r="S33" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="W33" s="41"/>
+      <c r="X33" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y33" s="56">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="56">
+        <v>0.2</v>
+      </c>
+      <c r="AB33" s="41"/>
+      <c r="AC33" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD33" s="56">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="56">
         <v>0.3</v>
       </c>
-      <c r="L29" s="58">
-        <v>0.45</v>
-      </c>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="R29" s="58">
+      <c r="AF33" s="64"/>
+    </row>
+    <row r="34" spans="1:32" ht="30.75" x14ac:dyDescent="0.9">
+      <c r="B34" s="53"/>
+      <c r="C34" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="35"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="P34" s="53"/>
+      <c r="Q34" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="R34" s="57"/>
+      <c r="S34" s="57"/>
+      <c r="W34" s="53"/>
+      <c r="X34" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y34" s="57"/>
+      <c r="Z34" s="57"/>
+      <c r="AB34" s="53"/>
+      <c r="AC34" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD34" s="57"/>
+      <c r="AE34" s="57"/>
+      <c r="AF34" s="60"/>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B35" s="41"/>
+      <c r="C35" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="E35" s="54">
+        <v>0.6</v>
+      </c>
+      <c r="I35" s="41"/>
+      <c r="J35" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" s="56">
+        <v>0</v>
+      </c>
+      <c r="L35" s="56">
+        <v>0.4</v>
+      </c>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="R35" s="56">
+        <v>0</v>
+      </c>
+      <c r="S35" s="56">
+        <v>0.4</v>
+      </c>
+      <c r="W35" s="41"/>
+      <c r="X35" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y35" s="56">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="56">
+        <v>0.4</v>
+      </c>
+      <c r="AB35" s="41"/>
+      <c r="AC35" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD35" s="56">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="56">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AF35" s="64"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B36" s="41"/>
+      <c r="C36" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="54">
+        <v>0.08</v>
+      </c>
+      <c r="E36" s="54">
+        <v>0.6</v>
+      </c>
+      <c r="I36" s="41"/>
+      <c r="J36" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="K36" s="56">
+        <v>0</v>
+      </c>
+      <c r="L36" s="56">
+        <v>0.4</v>
+      </c>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="R36" s="56">
+        <v>0</v>
+      </c>
+      <c r="S36" s="56">
         <v>0.3</v>
       </c>
-      <c r="S29" s="58">
-        <v>0.45</v>
-      </c>
-      <c r="W29" s="43"/>
-      <c r="X29" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y29" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="Z29" s="58">
-        <v>0.7</v>
-      </c>
-      <c r="AB29" s="43"/>
-      <c r="AC29" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD29" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="AE29" s="58">
-        <v>0.7</v>
-      </c>
-      <c r="AF29" s="66"/>
-      <c r="AG29" s="43"/>
-      <c r="AH29" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI29" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="AJ29" s="58">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B30" s="43"/>
-      <c r="C30" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="56">
+      <c r="W36" s="41"/>
+      <c r="X36" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y36" s="56">
         <v>0</v>
       </c>
-      <c r="E30" s="56">
-        <v>0.45</v>
-      </c>
-      <c r="I30" s="43"/>
-      <c r="J30" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="K30" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="L30" s="58">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="R30" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="S30" s="58">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="W30" s="43"/>
-      <c r="X30" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y30" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="Z30" s="58">
-        <v>0.7</v>
-      </c>
-      <c r="AB30" s="43"/>
-      <c r="AC30" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD30" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="AE30" s="58">
-        <v>0.7</v>
-      </c>
-      <c r="AF30" s="66"/>
-      <c r="AG30" s="43"/>
-      <c r="AH30" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI30" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="AJ30" s="58">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:36" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="43"/>
-      <c r="C31" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="56">
+      <c r="Z36" s="56">
+        <v>0.26</v>
+      </c>
+      <c r="AB36" s="41"/>
+      <c r="AC36" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD36" s="56">
         <v>0</v>
       </c>
-      <c r="E31" s="56">
-        <v>0.12</v>
-      </c>
-      <c r="I31" s="43"/>
-      <c r="J31" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="K31" s="58">
-        <v>0</v>
-      </c>
-      <c r="L31" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="R31" s="58">
-        <v>0</v>
-      </c>
-      <c r="S31" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="W31" s="43"/>
-      <c r="X31" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y31" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="AB31" s="43"/>
-      <c r="AC31" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD31" s="58">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="AF31" s="66"/>
-      <c r="AG31" s="43"/>
-      <c r="AH31" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI31" s="58">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="58">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B32" s="43"/>
-      <c r="C32" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="56">
-        <v>0</v>
-      </c>
-      <c r="E32" s="56">
-        <v>0.1</v>
-      </c>
-      <c r="I32" s="43"/>
-      <c r="J32" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="K32" s="58">
-        <v>0</v>
-      </c>
-      <c r="L32" s="58">
-        <v>0.08</v>
-      </c>
-      <c r="P32" s="43"/>
-      <c r="Q32" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="R32" s="58">
-        <v>0</v>
-      </c>
-      <c r="S32" s="58">
-        <v>0.08</v>
-      </c>
-      <c r="W32" s="43"/>
-      <c r="X32" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y32" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="AB32" s="43"/>
-      <c r="AC32" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD32" s="58">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="AF32" s="66"/>
-      <c r="AG32" s="43"/>
-      <c r="AH32" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI32" s="58">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="58">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:36" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="43"/>
-      <c r="C33" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="56">
-        <v>0</v>
-      </c>
-      <c r="E33" s="56">
-        <v>0.1</v>
-      </c>
-      <c r="I33" s="43"/>
-      <c r="J33" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="K33" s="58">
-        <v>0</v>
-      </c>
-      <c r="L33" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="R33" s="58">
-        <v>0</v>
-      </c>
-      <c r="S33" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="W33" s="43"/>
-      <c r="X33" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y33" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="AB33" s="43"/>
-      <c r="AC33" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD33" s="58">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="AF33" s="66"/>
-      <c r="AG33" s="43"/>
-      <c r="AH33" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI33" s="58">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="58">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:36" ht="30.75" x14ac:dyDescent="0.9">
-      <c r="B34" s="55"/>
-      <c r="C34" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="35"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="K34" s="59"/>
-      <c r="L34" s="59"/>
-      <c r="P34" s="55"/>
-      <c r="Q34" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="R34" s="59"/>
-      <c r="S34" s="59"/>
-      <c r="W34" s="55"/>
-      <c r="X34" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y34" s="59"/>
-      <c r="Z34" s="59"/>
-      <c r="AB34" s="55"/>
-      <c r="AC34" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD34" s="59"/>
-      <c r="AE34" s="59"/>
-      <c r="AF34" s="62"/>
-      <c r="AG34" s="55"/>
-      <c r="AH34" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI34" s="59"/>
-      <c r="AJ34" s="59"/>
-    </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B35" s="43"/>
-      <c r="C35" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="56">
-        <v>0.1</v>
-      </c>
-      <c r="E35" s="56">
-        <v>0.6</v>
-      </c>
-      <c r="I35" s="43"/>
-      <c r="J35" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="K35" s="58">
-        <v>0</v>
-      </c>
-      <c r="L35" s="58">
+      <c r="AE36" s="56">
+        <v>0.24</v>
+      </c>
+      <c r="AF36" s="64"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B37" s="41"/>
+      <c r="C37" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="54">
+        <v>0.01</v>
+      </c>
+      <c r="E37" s="54">
         <v>0.4</v>
       </c>
-      <c r="P35" s="43"/>
-      <c r="Q35" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="R35" s="58">
-        <v>0</v>
-      </c>
-      <c r="S35" s="58">
+      <c r="I37" s="41"/>
+      <c r="J37" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="K37" s="56">
+        <v>0.01</v>
+      </c>
+      <c r="L37" s="56">
         <v>0.4</v>
       </c>
-      <c r="W35" s="43"/>
-      <c r="X35" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y35" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="58">
-        <v>0.12</v>
-      </c>
-      <c r="AB35" s="43"/>
-      <c r="AC35" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD35" s="58">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="58">
-        <v>0.12</v>
-      </c>
-      <c r="AF35" s="66"/>
-      <c r="AG35" s="43"/>
-      <c r="AH35" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI35" s="58">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="58">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B36" s="43"/>
-      <c r="C36" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" s="56">
-        <v>0.08</v>
-      </c>
-      <c r="E36" s="56">
-        <v>0.6</v>
-      </c>
-      <c r="I36" s="43"/>
-      <c r="J36" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="K36" s="58">
-        <v>0</v>
-      </c>
-      <c r="L36" s="58">
-        <v>0.4</v>
-      </c>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="R36" s="58">
-        <v>0</v>
-      </c>
-      <c r="S36" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="W36" s="43"/>
-      <c r="X36" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y36" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="AB36" s="43"/>
-      <c r="AC36" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD36" s="58">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="AF36" s="66"/>
-      <c r="AG36" s="43"/>
-      <c r="AH36" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI36" s="58">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="58">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B37" s="43"/>
-      <c r="C37" s="53" t="s">
+      <c r="P37" s="41"/>
+      <c r="Q37" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="56">
+      <c r="R37" s="56">
         <v>0.01</v>
       </c>
-      <c r="E37" s="56">
-        <v>0.4</v>
-      </c>
-      <c r="I37" s="43"/>
-      <c r="J37" s="53" t="s">
+      <c r="S37" s="56">
+        <v>0.2</v>
+      </c>
+      <c r="W37" s="41"/>
+      <c r="X37" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="K37" s="58">
+      <c r="Y37" s="56">
         <v>0.01</v>
       </c>
-      <c r="L37" s="58">
-        <v>0.4</v>
-      </c>
-      <c r="P37" s="43"/>
-      <c r="Q37" s="53" t="s">
+      <c r="Z37" s="56">
+        <v>0.15</v>
+      </c>
+      <c r="AB37" s="41"/>
+      <c r="AC37" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="R37" s="58">
+      <c r="AD37" s="56">
         <v>0.01</v>
       </c>
-      <c r="S37" s="58">
-        <v>0.2</v>
-      </c>
-      <c r="W37" s="43"/>
-      <c r="X37" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y37" s="58">
-        <v>0.01</v>
-      </c>
-      <c r="Z37" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD37" s="58">
-        <v>0.01</v>
-      </c>
-      <c r="AE37" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="AF37" s="66"/>
-      <c r="AG37" s="43"/>
-      <c r="AH37" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI37" s="58">
-        <v>0.01</v>
-      </c>
-      <c r="AJ37" s="58">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B38" s="46"/>
-      <c r="C38" s="53" t="s">
+      <c r="AE37" s="56">
+        <v>0.15</v>
+      </c>
+      <c r="AF37" s="64"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B38" s="44"/>
+      <c r="C38" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="53" t="s">
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="K38" s="48"/>
-      <c r="L38" s="48"/>
-      <c r="P38" s="46"/>
-      <c r="Q38" s="53" t="s">
+      <c r="K38" s="46"/>
+      <c r="L38" s="46"/>
+      <c r="P38" s="44"/>
+      <c r="Q38" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="R38" s="48"/>
-      <c r="S38" s="48"/>
-      <c r="W38" s="46"/>
-      <c r="X38" s="53" t="s">
+      <c r="R38" s="46"/>
+      <c r="S38" s="46"/>
+      <c r="W38" s="44"/>
+      <c r="X38" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="Y38" s="48"/>
-      <c r="Z38" s="48"/>
-      <c r="AB38" s="46"/>
-      <c r="AC38" s="53" t="s">
+      <c r="Y38" s="46"/>
+      <c r="Z38" s="46"/>
+      <c r="AB38" s="44"/>
+      <c r="AC38" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="AD38" s="48"/>
-      <c r="AE38" s="48"/>
-      <c r="AF38" s="67"/>
-      <c r="AG38" s="46"/>
-      <c r="AH38" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI38" s="48"/>
-      <c r="AJ38" s="48"/>
-    </row>
-    <row r="39" spans="1:36" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="47"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="47"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="53"/>
-      <c r="R39" s="57"/>
-      <c r="S39" s="47"/>
-      <c r="W39" s="43"/>
-      <c r="X39" s="53"/>
-      <c r="Y39" s="57"/>
-      <c r="Z39" s="47"/>
-      <c r="AB39" s="43"/>
-      <c r="AC39" s="53"/>
-      <c r="AD39" s="57"/>
-      <c r="AE39" s="47"/>
-      <c r="AF39" s="49"/>
-      <c r="AG39" s="43"/>
-      <c r="AH39" s="53"/>
-      <c r="AI39" s="57"/>
-      <c r="AJ39" s="47"/>
-    </row>
-    <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="B40" s="55"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
+      <c r="AD38" s="46"/>
+      <c r="AE38" s="46"/>
+      <c r="AF38" s="65"/>
+    </row>
+    <row r="39" spans="1:32" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="45"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="51"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="45"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="51"/>
+      <c r="R39" s="55"/>
+      <c r="S39" s="45"/>
+      <c r="W39" s="41"/>
+      <c r="X39" s="51"/>
+      <c r="Y39" s="55"/>
+      <c r="Z39" s="45"/>
+      <c r="AB39" s="41"/>
+      <c r="AC39" s="51"/>
+      <c r="AD39" s="55"/>
+      <c r="AE39" s="45"/>
+      <c r="AF39" s="47"/>
+    </row>
+    <row r="40" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B40" s="53"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
       <c r="F40" s="35"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="53"/>
-      <c r="R40" s="55"/>
-      <c r="S40" s="55"/>
-      <c r="W40" s="55"/>
-      <c r="X40" s="53"/>
-      <c r="Y40" s="55"/>
-      <c r="Z40" s="55"/>
-      <c r="AB40" s="55"/>
-      <c r="AC40" s="53"/>
-      <c r="AD40" s="55"/>
-      <c r="AE40" s="55"/>
-      <c r="AF40" s="60"/>
-      <c r="AG40" s="55"/>
-      <c r="AH40" s="53"/>
-      <c r="AI40" s="55"/>
-      <c r="AJ40" s="55"/>
-    </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="B41" s="50">
+      <c r="I40" s="53"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
+      <c r="P40" s="53"/>
+      <c r="Q40" s="51"/>
+      <c r="R40" s="53"/>
+      <c r="S40" s="53"/>
+      <c r="W40" s="53"/>
+      <c r="X40" s="51"/>
+      <c r="Y40" s="53"/>
+      <c r="Z40" s="53"/>
+      <c r="AB40" s="53"/>
+      <c r="AC40" s="51"/>
+      <c r="AD40" s="53"/>
+      <c r="AE40" s="53"/>
+      <c r="AF40" s="58"/>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B41" s="48">
         <v>1</v>
       </c>
-      <c r="C41" s="53" t="s">
+      <c r="C41" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="D41" s="51">
+      <c r="D41" s="49">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="E41" s="51"/>
-      <c r="I41" s="50">
+      <c r="E41" s="49"/>
+      <c r="I41" s="48">
         <v>1</v>
       </c>
-      <c r="J41" s="53" t="s">
+      <c r="J41" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="K41" s="78">
+      <c r="K41" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="L41" s="78"/>
-      <c r="P41" s="50">
+      <c r="L41" s="77"/>
+      <c r="P41" s="48">
         <v>1</v>
       </c>
-      <c r="Q41" s="53" t="s">
+      <c r="Q41" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="R41" s="78">
+      <c r="R41" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="S41" s="78"/>
-      <c r="W41" s="50">
+      <c r="S41" s="77"/>
+      <c r="W41" s="48">
         <v>1</v>
       </c>
-      <c r="X41" s="53" t="s">
+      <c r="X41" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="Y41" s="78">
+      <c r="Y41" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Z41" s="78"/>
-      <c r="AB41" s="50">
+      <c r="Z41" s="77"/>
+      <c r="AB41" s="48">
         <v>1</v>
       </c>
-      <c r="AC41" s="53" t="s">
+      <c r="AC41" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="AD41" s="78">
+      <c r="AD41" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="AE41" s="78"/>
-      <c r="AF41" s="68"/>
-      <c r="AG41" s="50">
-        <v>1</v>
-      </c>
-      <c r="AH41" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="AI41" s="78">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="AJ41" s="78"/>
-    </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A43" s="52"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="52"/>
-      <c r="P43" s="52"/>
-      <c r="Q43" s="52"/>
-      <c r="R43" s="52"/>
-      <c r="W43" s="52"/>
-      <c r="X43" s="52"/>
-      <c r="Y43" s="52"/>
-      <c r="AB43" s="52"/>
-      <c r="AC43" s="52"/>
-      <c r="AD43" s="52"/>
-      <c r="AG43" s="52"/>
-      <c r="AH43" s="52"/>
-      <c r="AI43" s="52"/>
-    </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A44" s="52"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="P44" s="52"/>
-      <c r="Q44" s="52"/>
-      <c r="R44" s="52"/>
-      <c r="W44" s="52"/>
-      <c r="X44" s="52"/>
-      <c r="Y44" s="52"/>
-      <c r="AB44" s="52"/>
-      <c r="AC44" s="52"/>
-      <c r="AD44" s="52"/>
-      <c r="AG44" s="52"/>
-      <c r="AH44" s="52"/>
-      <c r="AI44" s="52"/>
-    </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A45" s="52"/>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="52"/>
-      <c r="P45" s="52"/>
-      <c r="Q45" s="52"/>
-      <c r="R45" s="52"/>
-      <c r="W45" s="52"/>
-      <c r="X45" s="52"/>
-      <c r="Y45" s="52"/>
-      <c r="AB45" s="52"/>
-      <c r="AC45" s="52"/>
-      <c r="AD45" s="52"/>
-      <c r="AG45" s="52"/>
-      <c r="AH45" s="52"/>
-      <c r="AI45" s="52"/>
-    </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A46" s="52"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="P46" s="52"/>
-      <c r="Q46" s="52"/>
-      <c r="R46" s="52"/>
-      <c r="W46" s="52"/>
-      <c r="X46" s="52"/>
-      <c r="Y46" s="52"/>
-      <c r="AB46" s="52"/>
-      <c r="AC46" s="52"/>
-      <c r="AD46" s="52"/>
-      <c r="AG46" s="52"/>
-      <c r="AH46" s="52"/>
-      <c r="AI46" s="52"/>
-    </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A47" s="52"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="P47" s="52"/>
-      <c r="Q47" s="52"/>
-      <c r="R47" s="52"/>
-      <c r="W47" s="52"/>
-      <c r="X47" s="52"/>
-      <c r="Y47" s="52"/>
-      <c r="AB47" s="52"/>
-      <c r="AC47" s="52"/>
-      <c r="AD47" s="52"/>
-      <c r="AG47" s="52"/>
-      <c r="AH47" s="52"/>
-      <c r="AI47" s="52"/>
-    </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="A48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="52"/>
-      <c r="P48" s="52"/>
-      <c r="Q48" s="52"/>
-      <c r="R48" s="52"/>
-      <c r="W48" s="52"/>
-      <c r="X48" s="52"/>
-      <c r="Y48" s="52"/>
-      <c r="AB48" s="52"/>
-      <c r="AC48" s="52"/>
-      <c r="AD48" s="52"/>
-      <c r="AG48" s="52"/>
-      <c r="AH48" s="52"/>
-      <c r="AI48" s="52"/>
-    </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A49" s="52"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="52"/>
-      <c r="K49" s="52"/>
-      <c r="P49" s="52"/>
-      <c r="Q49" s="52"/>
-      <c r="R49" s="52"/>
-      <c r="W49" s="52"/>
-      <c r="X49" s="52"/>
-      <c r="Y49" s="52"/>
-      <c r="AB49" s="52"/>
-      <c r="AC49" s="52"/>
-      <c r="AD49" s="52"/>
-      <c r="AG49" s="52"/>
-      <c r="AH49" s="52"/>
-      <c r="AI49" s="52"/>
-    </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="I50" s="52"/>
-      <c r="J50" s="52"/>
-      <c r="K50" s="52"/>
-      <c r="P50" s="52"/>
-      <c r="Q50" s="52"/>
-      <c r="R50" s="52"/>
-      <c r="W50" s="52"/>
-      <c r="X50" s="52"/>
-      <c r="Y50" s="52"/>
-      <c r="AB50" s="52"/>
-      <c r="AC50" s="52"/>
-      <c r="AD50" s="52"/>
-      <c r="AG50" s="52"/>
-      <c r="AH50" s="52"/>
-      <c r="AI50" s="52"/>
-    </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A51" s="52"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
-      <c r="P51" s="52"/>
-      <c r="Q51" s="52"/>
-      <c r="R51" s="52"/>
-      <c r="W51" s="52"/>
-      <c r="X51" s="52"/>
-      <c r="Y51" s="52"/>
-      <c r="AB51" s="52"/>
-      <c r="AC51" s="52"/>
-      <c r="AD51" s="52"/>
-      <c r="AG51" s="52"/>
-      <c r="AH51" s="52"/>
-      <c r="AI51" s="52"/>
-    </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
-      <c r="K52" s="52"/>
-      <c r="P52" s="52"/>
-      <c r="Q52" s="52"/>
-      <c r="R52" s="52"/>
-      <c r="W52" s="52"/>
-      <c r="X52" s="52"/>
-      <c r="Y52" s="52"/>
-      <c r="AB52" s="52"/>
-      <c r="AC52" s="52"/>
-      <c r="AD52" s="52"/>
-      <c r="AG52" s="52"/>
-      <c r="AH52" s="52"/>
-      <c r="AI52" s="52"/>
-    </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="I53" s="52"/>
-      <c r="J53" s="52"/>
-      <c r="K53" s="52"/>
-      <c r="P53" s="52"/>
-      <c r="Q53" s="52"/>
-      <c r="R53" s="52"/>
-      <c r="W53" s="52"/>
-      <c r="X53" s="52"/>
-      <c r="Y53" s="52"/>
-      <c r="AB53" s="52"/>
-      <c r="AC53" s="52"/>
-      <c r="AD53" s="52"/>
-      <c r="AG53" s="52"/>
-      <c r="AH53" s="52"/>
-      <c r="AI53" s="52"/>
-    </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A54" s="52"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
-      <c r="I54" s="52"/>
-      <c r="J54" s="52"/>
-      <c r="K54" s="52"/>
-      <c r="P54" s="52"/>
-      <c r="Q54" s="52"/>
-      <c r="R54" s="52"/>
-      <c r="W54" s="52"/>
-      <c r="X54" s="52"/>
-      <c r="Y54" s="52"/>
-      <c r="AB54" s="52"/>
-      <c r="AC54" s="52"/>
-      <c r="AD54" s="52"/>
-      <c r="AG54" s="52"/>
-      <c r="AH54" s="52"/>
-      <c r="AI54" s="52"/>
-    </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A55" s="52"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="I55" s="52"/>
-      <c r="J55" s="52"/>
-      <c r="K55" s="52"/>
-      <c r="P55" s="52"/>
-      <c r="Q55" s="52"/>
-      <c r="R55" s="52"/>
-      <c r="W55" s="52"/>
-      <c r="X55" s="52"/>
-      <c r="Y55" s="52"/>
-      <c r="AB55" s="52"/>
-      <c r="AC55" s="52"/>
-      <c r="AD55" s="52"/>
-      <c r="AG55" s="52"/>
-      <c r="AH55" s="52"/>
-      <c r="AI55" s="52"/>
-    </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A56" s="52"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="I56" s="52"/>
-      <c r="J56" s="52"/>
-      <c r="K56" s="52"/>
-      <c r="P56" s="52"/>
-      <c r="Q56" s="52"/>
-      <c r="R56" s="52"/>
-      <c r="W56" s="52"/>
-      <c r="X56" s="52"/>
-      <c r="Y56" s="52"/>
-      <c r="AB56" s="52"/>
-      <c r="AC56" s="52"/>
-      <c r="AD56" s="52"/>
-      <c r="AG56" s="52"/>
-      <c r="AH56" s="52"/>
-      <c r="AI56" s="52"/>
-    </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A57" s="52"/>
-      <c r="C57" s="52"/>
-      <c r="D57" s="52"/>
-      <c r="I57" s="52"/>
-      <c r="J57" s="52"/>
-      <c r="K57" s="52"/>
-      <c r="P57" s="52"/>
-      <c r="Q57" s="52"/>
-      <c r="R57" s="52"/>
-      <c r="W57" s="52"/>
-      <c r="X57" s="52"/>
-      <c r="Y57" s="52"/>
-      <c r="AB57" s="52"/>
-      <c r="AC57" s="52"/>
-      <c r="AD57" s="52"/>
-      <c r="AG57" s="52"/>
-      <c r="AH57" s="52"/>
-      <c r="AI57" s="52"/>
-    </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A58" s="52"/>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="P58" s="52"/>
-      <c r="Q58" s="52"/>
-      <c r="R58" s="52"/>
-      <c r="W58" s="52"/>
-      <c r="X58" s="52"/>
-      <c r="Y58" s="52"/>
-      <c r="AB58" s="52"/>
-      <c r="AC58" s="52"/>
-      <c r="AD58" s="52"/>
-      <c r="AG58" s="52"/>
-      <c r="AH58" s="52"/>
-      <c r="AI58" s="52"/>
-    </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A59" s="52"/>
-      <c r="B59" s="52"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-    </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A60" s="52"/>
-      <c r="B60" s="52"/>
-      <c r="C60" s="52"/>
-      <c r="D60" s="52"/>
+      <c r="AE41" s="77"/>
+      <c r="AF41" s="66"/>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A43" s="50"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="W43" s="50"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="50"/>
+      <c r="AB43" s="50"/>
+      <c r="AC43" s="50"/>
+      <c r="AD43" s="50"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A44" s="50"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="P44" s="50"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50"/>
+      <c r="W44" s="50"/>
+      <c r="X44" s="50"/>
+      <c r="Y44" s="50"/>
+      <c r="AB44" s="50"/>
+      <c r="AC44" s="50"/>
+      <c r="AD44" s="50"/>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A45" s="50"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="P45" s="50"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50"/>
+      <c r="W45" s="50"/>
+      <c r="X45" s="50"/>
+      <c r="Y45" s="50"/>
+      <c r="AB45" s="50"/>
+      <c r="AC45" s="50"/>
+      <c r="AD45" s="50"/>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A46" s="50"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="50"/>
+      <c r="I46" s="50"/>
+      <c r="J46" s="50"/>
+      <c r="K46" s="50"/>
+      <c r="P46" s="50"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50"/>
+      <c r="W46" s="50"/>
+      <c r="X46" s="50"/>
+      <c r="Y46" s="50"/>
+      <c r="AB46" s="50"/>
+      <c r="AC46" s="50"/>
+      <c r="AD46" s="50"/>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A47" s="50"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="50"/>
+      <c r="I47" s="50"/>
+      <c r="J47" s="50"/>
+      <c r="K47" s="50"/>
+      <c r="P47" s="50"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50"/>
+      <c r="W47" s="50"/>
+      <c r="X47" s="50"/>
+      <c r="Y47" s="50"/>
+      <c r="AB47" s="50"/>
+      <c r="AC47" s="50"/>
+      <c r="AD47" s="50"/>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A48" s="50"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50"/>
+      <c r="I48" s="50"/>
+      <c r="J48" s="50"/>
+      <c r="K48" s="50"/>
+      <c r="P48" s="50"/>
+      <c r="Q48" s="50"/>
+      <c r="R48" s="50"/>
+      <c r="W48" s="50"/>
+      <c r="X48" s="50"/>
+      <c r="Y48" s="50"/>
+      <c r="AB48" s="50"/>
+      <c r="AC48" s="50"/>
+      <c r="AD48" s="50"/>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A49" s="50"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="50"/>
+      <c r="P49" s="50"/>
+      <c r="Q49" s="50"/>
+      <c r="R49" s="50"/>
+      <c r="W49" s="50"/>
+      <c r="X49" s="50"/>
+      <c r="Y49" s="50"/>
+      <c r="AB49" s="50"/>
+      <c r="AC49" s="50"/>
+      <c r="AD49" s="50"/>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A50" s="50"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="50"/>
+      <c r="K50" s="50"/>
+      <c r="P50" s="50"/>
+      <c r="Q50" s="50"/>
+      <c r="R50" s="50"/>
+      <c r="W50" s="50"/>
+      <c r="X50" s="50"/>
+      <c r="Y50" s="50"/>
+      <c r="AB50" s="50"/>
+      <c r="AC50" s="50"/>
+      <c r="AD50" s="50"/>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A51" s="50"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="I51" s="50"/>
+      <c r="J51" s="50"/>
+      <c r="K51" s="50"/>
+      <c r="P51" s="50"/>
+      <c r="Q51" s="50"/>
+      <c r="R51" s="50"/>
+      <c r="W51" s="50"/>
+      <c r="X51" s="50"/>
+      <c r="Y51" s="50"/>
+      <c r="AB51" s="50"/>
+      <c r="AC51" s="50"/>
+      <c r="AD51" s="50"/>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A52" s="50"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="I52" s="50"/>
+      <c r="J52" s="50"/>
+      <c r="K52" s="50"/>
+      <c r="P52" s="50"/>
+      <c r="Q52" s="50"/>
+      <c r="R52" s="50"/>
+      <c r="W52" s="50"/>
+      <c r="X52" s="50"/>
+      <c r="Y52" s="50"/>
+      <c r="AB52" s="50"/>
+      <c r="AC52" s="50"/>
+      <c r="AD52" s="50"/>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A53" s="50"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="50"/>
+      <c r="I53" s="50"/>
+      <c r="J53" s="50"/>
+      <c r="K53" s="50"/>
+      <c r="P53" s="50"/>
+      <c r="Q53" s="50"/>
+      <c r="R53" s="50"/>
+      <c r="W53" s="50"/>
+      <c r="X53" s="50"/>
+      <c r="Y53" s="50"/>
+      <c r="AB53" s="50"/>
+      <c r="AC53" s="50"/>
+      <c r="AD53" s="50"/>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A54" s="50"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="50"/>
+      <c r="I54" s="50"/>
+      <c r="J54" s="50"/>
+      <c r="K54" s="50"/>
+      <c r="P54" s="50"/>
+      <c r="Q54" s="50"/>
+      <c r="R54" s="50"/>
+      <c r="W54" s="50"/>
+      <c r="X54" s="50"/>
+      <c r="Y54" s="50"/>
+      <c r="AB54" s="50"/>
+      <c r="AC54" s="50"/>
+      <c r="AD54" s="50"/>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A55" s="50"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="I55" s="50"/>
+      <c r="J55" s="50"/>
+      <c r="K55" s="50"/>
+      <c r="P55" s="50"/>
+      <c r="Q55" s="50"/>
+      <c r="R55" s="50"/>
+      <c r="W55" s="50"/>
+      <c r="X55" s="50"/>
+      <c r="Y55" s="50"/>
+      <c r="AB55" s="50"/>
+      <c r="AC55" s="50"/>
+      <c r="AD55" s="50"/>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A56" s="50"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="50"/>
+      <c r="P56" s="50"/>
+      <c r="Q56" s="50"/>
+      <c r="R56" s="50"/>
+      <c r="W56" s="50"/>
+      <c r="X56" s="50"/>
+      <c r="Y56" s="50"/>
+      <c r="AB56" s="50"/>
+      <c r="AC56" s="50"/>
+      <c r="AD56" s="50"/>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A57" s="50"/>
+      <c r="C57" s="50"/>
+      <c r="D57" s="50"/>
+      <c r="I57" s="50"/>
+      <c r="J57" s="50"/>
+      <c r="K57" s="50"/>
+      <c r="P57" s="50"/>
+      <c r="Q57" s="50"/>
+      <c r="R57" s="50"/>
+      <c r="W57" s="50"/>
+      <c r="X57" s="50"/>
+      <c r="Y57" s="50"/>
+      <c r="AB57" s="50"/>
+      <c r="AC57" s="50"/>
+      <c r="AD57" s="50"/>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A58" s="50"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
+      <c r="K58" s="50"/>
+      <c r="P58" s="50"/>
+      <c r="Q58" s="50"/>
+      <c r="R58" s="50"/>
+      <c r="W58" s="50"/>
+      <c r="X58" s="50"/>
+      <c r="Y58" s="50"/>
+      <c r="AB58" s="50"/>
+      <c r="AC58" s="50"/>
+      <c r="AD58" s="50"/>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A59" s="50"/>
+      <c r="B59" s="50"/>
+      <c r="C59" s="50"/>
+      <c r="D59" s="50"/>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A60" s="50"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="AI41:AJ41"/>
+  <mergeCells count="4">
     <mergeCell ref="AD41:AE41"/>
     <mergeCell ref="Y41:Z41"/>
     <mergeCell ref="R41:S41"/>
@@ -4869,361 +4554,473 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EEFEB08-95BB-4F2C-A774-ABE971D64740}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A3:J46"/>
+  <dimension ref="A3:T46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="22" t="s">
-        <v>236</v>
-      </c>
+    <row r="3" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="22" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
       <c r="H3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22" t="s">
+      <c r="E4" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="H4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A5" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="B5" s="73">
+        <v>0.98</v>
+      </c>
+      <c r="C5" s="73">
+        <v>0.98136999999999996</v>
+      </c>
+      <c r="D5" s="73">
+        <v>1</v>
+      </c>
+      <c r="E5" s="73">
+        <v>0.97318199999999999</v>
+      </c>
+      <c r="F5" s="73">
+        <v>0.98301400000000005</v>
+      </c>
+      <c r="G5" s="73">
+        <v>1</v>
+      </c>
+      <c r="H5" s="72">
+        <v>0.97697900000000004</v>
+      </c>
+      <c r="I5" s="72">
+        <v>0.97702699999999998</v>
+      </c>
+      <c r="J5" s="73">
+        <v>0.97935300000000003</v>
+      </c>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="72"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A6" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="B6" s="73">
+        <v>0.97</v>
+      </c>
+      <c r="C6" s="73">
+        <v>0.97494199999999998</v>
+      </c>
+      <c r="D6" s="73">
+        <v>1</v>
+      </c>
+      <c r="E6" s="73">
+        <v>0.96114100000000002</v>
+      </c>
+      <c r="F6" s="73">
+        <v>0.96215399999999995</v>
+      </c>
+      <c r="G6" s="73">
+        <v>1</v>
+      </c>
+      <c r="H6" s="72">
+        <v>0.95487599999999995</v>
+      </c>
+      <c r="I6" s="72">
+        <v>0.96137700000000004</v>
+      </c>
+      <c r="J6" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A7" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="H4" t="s">
-        <v>240</v>
-      </c>
-      <c r="I4" t="s">
-        <v>241</v>
-      </c>
-      <c r="J4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="22" t="s">
+      <c r="B7" s="73">
+        <v>0.96</v>
+      </c>
+      <c r="C7" s="73">
+        <v>0.96625399999999995</v>
+      </c>
+      <c r="D7" s="73">
+        <v>1</v>
+      </c>
+      <c r="E7" s="73">
+        <v>0.95528299999999999</v>
+      </c>
+      <c r="F7" s="73">
+        <v>0.95889100000000005</v>
+      </c>
+      <c r="G7" s="73">
+        <v>1</v>
+      </c>
+      <c r="H7" s="72">
+        <v>0.94988799999999995</v>
+      </c>
+      <c r="I7" s="72">
+        <v>0.95862999999999998</v>
+      </c>
+      <c r="J7" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="72"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A8" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="B5" s="75">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="C5" s="75">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="D5" s="75">
-        <v>1.4E-3</v>
-      </c>
-      <c r="E5" s="75">
-        <v>1.8E-3</v>
-      </c>
-      <c r="F5" s="75">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="G5" s="75">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="H5" s="74">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="I5" s="74">
-        <v>4.7999999999999996E-3</v>
-      </c>
-      <c r="J5" s="74">
-        <v>5.5999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="22" t="s">
+      <c r="B8" s="73">
+        <v>0.97</v>
+      </c>
+      <c r="C8" s="73">
+        <v>0.97522600000000004</v>
+      </c>
+      <c r="D8" s="73">
+        <v>1</v>
+      </c>
+      <c r="E8" s="73">
+        <v>0.96273900000000001</v>
+      </c>
+      <c r="F8" s="73">
+        <v>0.97137799999999996</v>
+      </c>
+      <c r="G8" s="73">
+        <v>1</v>
+      </c>
+      <c r="H8" s="72">
+        <v>0.96641900000000003</v>
+      </c>
+      <c r="I8" s="72">
+        <v>0.97198499999999999</v>
+      </c>
+      <c r="J8" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A9" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="B6" s="75">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="C6" s="75">
-        <v>1.4E-3</v>
-      </c>
-      <c r="D6" s="75">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="E6" s="75">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="F6" s="75">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G6" s="75">
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="H6" s="74">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="I6" s="74">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="J6" s="74">
-        <v>6.4000000000000003E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="22" t="s">
+      <c r="B9" s="73">
+        <v>0.98</v>
+      </c>
+      <c r="C9" s="73">
+        <v>0.98994400000000005</v>
+      </c>
+      <c r="D9" s="73">
+        <v>1</v>
+      </c>
+      <c r="E9" s="73">
+        <v>0.97648900000000005</v>
+      </c>
+      <c r="F9" s="73">
+        <v>0.98408499999999999</v>
+      </c>
+      <c r="G9" s="73">
+        <v>1</v>
+      </c>
+      <c r="H9" s="72">
+        <v>0.98188500000000001</v>
+      </c>
+      <c r="I9" s="72">
+        <v>0.98509500000000005</v>
+      </c>
+      <c r="J9" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="72"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A10" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="75">
-        <v>1E-3</v>
-      </c>
-      <c r="C7" s="75">
-        <v>1.5E-3</v>
-      </c>
-      <c r="D7" s="75">
-        <v>1.9E-3</v>
-      </c>
-      <c r="E7" s="75">
-        <v>2.3999999999999998E-3</v>
-      </c>
-      <c r="F7" s="75">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="G7" s="75">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H7" s="74">
-        <v>4.5999999999999999E-3</v>
-      </c>
-      <c r="I7" s="74">
-        <v>6.3E-3</v>
-      </c>
-      <c r="J7" s="74">
-        <v>7.1999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="22" t="s">
+      <c r="B10" s="73">
+        <v>0.96</v>
+      </c>
+      <c r="C10" s="73">
+        <v>0.967445</v>
+      </c>
+      <c r="D10" s="73">
+        <v>1</v>
+      </c>
+      <c r="E10" s="73">
+        <v>0.95294900000000005</v>
+      </c>
+      <c r="F10" s="73">
+        <v>0.95658799999999999</v>
+      </c>
+      <c r="G10" s="73">
+        <v>1</v>
+      </c>
+      <c r="H10" s="72">
+        <v>0.952627</v>
+      </c>
+      <c r="I10" s="72">
+        <v>0.96184199999999997</v>
+      </c>
+      <c r="J10" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A11" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="B8" s="75">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="C8" s="75">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="D8" s="75">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="E8" s="75">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="F8" s="75">
-        <v>3.8E-3</v>
-      </c>
-      <c r="G8" s="75">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="H8" s="74">
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="I8" s="74">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="J8" s="74">
-        <v>7.9000000000000008E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="22" t="s">
+      <c r="B11" s="73">
+        <v>0.98</v>
+      </c>
+      <c r="C11" s="73">
+        <v>0.98329100000000003</v>
+      </c>
+      <c r="D11" s="73">
+        <v>1</v>
+      </c>
+      <c r="E11" s="73">
+        <v>0.97331299999999998</v>
+      </c>
+      <c r="F11" s="73">
+        <v>0.97338800000000003</v>
+      </c>
+      <c r="G11" s="73">
+        <v>1</v>
+      </c>
+      <c r="H11" s="72">
+        <v>0.96800699999999995</v>
+      </c>
+      <c r="I11" s="72">
+        <v>0.97628899999999996</v>
+      </c>
+      <c r="J11" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="72"/>
+    </row>
+    <row r="12" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="B9" s="75">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="C9" s="75">
-        <v>1.9E-3</v>
-      </c>
-      <c r="D9" s="75">
-        <v>2.3E-3</v>
-      </c>
-      <c r="E9" s="75">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="F9" s="75">
-        <v>4.3E-3</v>
-      </c>
-      <c r="G9" s="75">
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="H9" s="74">
-        <v>5.7999999999999996E-3</v>
-      </c>
-      <c r="I9" s="74">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="J9" s="74">
-        <v>9.1000000000000004E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="B10" s="75">
-        <v>1.4E-3</v>
-      </c>
-      <c r="C10" s="75">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="D10" s="75">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="E10" s="75">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="F10" s="75">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="G10" s="75">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="H10" s="74">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="I10" s="74">
-        <v>8.6E-3</v>
-      </c>
-      <c r="J10" s="74">
-        <v>9.9000000000000008E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="B11" s="75">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="C11" s="75">
-        <v>2.3E-3</v>
-      </c>
-      <c r="D11" s="75">
-        <v>2.8E-3</v>
-      </c>
-      <c r="E11" s="75">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="F11" s="75">
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="G11" s="75">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="H11" s="74">
-        <v>6.7999999999999996E-3</v>
-      </c>
-      <c r="I11" s="74">
-        <v>9.1999999999999998E-3</v>
-      </c>
-      <c r="J11" s="74">
-        <v>1.06E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="B12" s="75">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="C12" s="75">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="D12" s="75">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="E12" s="75">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="F12" s="75">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="G12" s="75">
-        <v>6.3E-3</v>
-      </c>
-      <c r="H12" s="74">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="I12" s="74">
-        <v>1.01E-2</v>
-      </c>
-      <c r="J12" s="74">
-        <v>1.15E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="73">
+        <v>0.96</v>
+      </c>
+      <c r="C12" s="73">
+        <v>0.96902299999999997</v>
+      </c>
+      <c r="D12" s="73">
+        <v>1</v>
+      </c>
+      <c r="E12" s="73">
+        <v>0.95867400000000003</v>
+      </c>
+      <c r="F12" s="73">
+        <v>0.96173299999999995</v>
+      </c>
+      <c r="G12" s="73">
+        <v>1</v>
+      </c>
+      <c r="H12" s="72">
+        <v>0.96093300000000004</v>
+      </c>
+      <c r="I12" s="72">
+        <v>0.96435599999999999</v>
+      </c>
+      <c r="J12" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+    </row>
+    <row r="13" spans="1:20" ht="63" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="B13" s="75">
-        <v>1.8E-3</v>
-      </c>
-      <c r="C13" s="75">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="D13" s="75">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="E13" s="75">
-        <v>4.3E-3</v>
-      </c>
-      <c r="F13" s="75">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="G13" s="75">
-        <v>6.7999999999999996E-3</v>
-      </c>
-      <c r="H13" s="74">
-        <v>8.2000000000000007E-3</v>
-      </c>
-      <c r="I13" s="74">
-        <v>1.11E-2</v>
-      </c>
-      <c r="J13" s="74">
-        <v>1.2699999999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+        <v>260</v>
+      </c>
+      <c r="B13" s="73">
+        <v>0.96</v>
+      </c>
+      <c r="C13" s="73">
+        <v>0.964086</v>
+      </c>
+      <c r="D13" s="73">
+        <v>1</v>
+      </c>
+      <c r="E13" s="73">
+        <v>0.95851399999999998</v>
+      </c>
+      <c r="F13" s="73">
+        <v>0.95943000000000001</v>
+      </c>
+      <c r="G13" s="73">
+        <v>1</v>
+      </c>
+      <c r="H13" s="72">
+        <v>0.95672199999999996</v>
+      </c>
+      <c r="I13" s="72">
+        <v>0.96389400000000003</v>
+      </c>
+      <c r="J13" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
+      <c r="T13" s="72"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A14" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="73">
+        <v>0.97</v>
+      </c>
+      <c r="C14" s="73">
+        <v>0.97101700000000002</v>
+      </c>
+      <c r="D14" s="73">
+        <v>1</v>
+      </c>
+      <c r="E14" s="73">
+        <v>0.969024</v>
+      </c>
+      <c r="F14" s="73">
+        <v>0.97461699999999996</v>
+      </c>
+      <c r="G14" s="73">
+        <v>1</v>
+      </c>
+      <c r="H14" s="72">
+        <v>0.97419299999999998</v>
+      </c>
+      <c r="I14" s="72">
+        <v>0.98317399999999999</v>
+      </c>
+      <c r="J14" s="73">
+        <v>0.98982199999999998</v>
+      </c>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="22"/>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -5232,7 +5029,7 @@
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -5281,13 +5078,13 @@
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>78</v>
       </c>
@@ -5297,190 +5094,190 @@
         <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H5" t="s">
         <v>68</v>
       </c>
       <c r="J5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B7" s="74">
+        <v>254</v>
+      </c>
+      <c r="B7" s="72">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="C7" s="74">
+      <c r="C7" s="72">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="72">
         <v>7.8E-2</v>
       </c>
-      <c r="E7" s="74">
+      <c r="E7" s="72">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="F7" s="74">
+      <c r="F7" s="72">
         <v>0.104</v>
       </c>
-      <c r="G7" s="74">
+      <c r="G7" s="72">
         <v>0.10199999999999999</v>
       </c>
-      <c r="H7" s="74">
+      <c r="H7" s="72">
         <v>0.13100000000000001</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="72">
         <v>0.13300000000000001</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="72">
         <v>0.152</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="72">
         <v>0.15</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="74">
+        <v>255</v>
+      </c>
+      <c r="B8" s="72">
         <v>-3.1E-2</v>
       </c>
-      <c r="C8" s="74">
+      <c r="C8" s="72">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="72">
         <v>-6.2E-2</v>
       </c>
-      <c r="E8" s="74">
+      <c r="E8" s="72">
         <v>-6.0999999999999999E-2</v>
       </c>
-      <c r="F8" s="74">
+      <c r="F8" s="72">
         <v>-8.4000000000000005E-2</v>
       </c>
-      <c r="G8" s="74">
+      <c r="G8" s="72">
         <v>-8.3000000000000004E-2</v>
       </c>
-      <c r="H8" s="74">
+      <c r="H8" s="72">
         <v>-0.107</v>
       </c>
-      <c r="I8" s="74">
+      <c r="I8" s="72">
         <v>-0.108</v>
       </c>
-      <c r="J8" s="74">
+      <c r="J8" s="72">
         <v>-0.121</v>
       </c>
-      <c r="K8" s="74">
+      <c r="K8" s="72">
         <v>-0.12</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" s="74">
+        <v>256</v>
+      </c>
+      <c r="B9" s="72">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="C9" s="74">
+      <c r="C9" s="72">
         <v>-1.9E-2</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="72">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="E9" s="74">
+      <c r="E9" s="72">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="F9" s="74">
+      <c r="F9" s="72">
         <v>-4.5999999999999999E-2</v>
       </c>
-      <c r="G9" s="74">
+      <c r="G9" s="72">
         <v>-4.4999999999999998E-2</v>
       </c>
-      <c r="H9" s="74">
+      <c r="H9" s="72">
         <v>-5.7000000000000002E-2</v>
       </c>
-      <c r="I9" s="74">
+      <c r="I9" s="72">
         <v>-5.8000000000000003E-2</v>
       </c>
-      <c r="J9" s="74">
+      <c r="J9" s="72">
         <v>-7.1999999999999995E-2</v>
       </c>
-      <c r="K9" s="74">
+      <c r="K9" s="72">
         <v>-7.0999999999999994E-2</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>261</v>
-      </c>
-      <c r="B10" s="74">
+        <v>257</v>
+      </c>
+      <c r="B10" s="72">
         <v>2.4E-2</v>
       </c>
-      <c r="C10" s="74">
+      <c r="C10" s="72">
         <v>2.3E-2</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="72">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E10" s="74">
+      <c r="E10" s="72">
         <v>3.9E-2</v>
       </c>
-      <c r="F10" s="74">
+      <c r="F10" s="72">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="G10" s="74">
+      <c r="G10" s="72">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="H10" s="74">
+      <c r="H10" s="72">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="I10" s="74">
+      <c r="I10" s="72">
         <v>6.3E-2</v>
       </c>
-      <c r="J10" s="74">
+      <c r="J10" s="72">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="K10" s="74">
+      <c r="K10" s="72">
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
@@ -5488,34 +5285,34 @@
       <c r="A11" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="74">
+      <c r="B11" s="72">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="C11" s="74">
+      <c r="C11" s="72">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="72">
         <v>-1.4E-2</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E11" s="72">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="F11" s="74">
+      <c r="F11" s="72">
         <v>-2.3E-2</v>
       </c>
-      <c r="G11" s="74">
+      <c r="G11" s="72">
         <v>-2.1999999999999999E-2</v>
       </c>
-      <c r="H11" s="74">
+      <c r="H11" s="72">
         <v>-3.1E-2</v>
       </c>
-      <c r="I11" s="74">
+      <c r="I11" s="72">
         <v>-0.03</v>
       </c>
-      <c r="J11" s="74">
+      <c r="J11" s="72">
         <v>-4.2000000000000003E-2</v>
       </c>
-      <c r="K11" s="74">
+      <c r="K11" s="72">
         <v>-4.1000000000000002E-2</v>
       </c>
     </row>
@@ -5523,69 +5320,69 @@
       <c r="A12" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="74">
+      <c r="B12" s="72">
         <v>-5.1999999999999998E-2</v>
       </c>
-      <c r="C12" s="74">
+      <c r="C12" s="72">
         <v>-5.0999999999999997E-2</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="72">
         <v>-9.8000000000000004E-2</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="72">
         <v>-9.7000000000000003E-2</v>
       </c>
-      <c r="F12" s="74">
+      <c r="F12" s="72">
         <v>-0.13400000000000001</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="72">
         <v>-0.13200000000000001</v>
       </c>
-      <c r="H12" s="74">
+      <c r="H12" s="72">
         <v>-0.17100000000000001</v>
       </c>
-      <c r="I12" s="74">
+      <c r="I12" s="72">
         <v>-0.17299999999999999</v>
       </c>
-      <c r="J12" s="74">
+      <c r="J12" s="72">
         <v>-0.20399999999999999</v>
       </c>
-      <c r="K12" s="74">
+      <c r="K12" s="72">
         <v>-0.20200000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>262</v>
-      </c>
-      <c r="B13" s="74">
+        <v>258</v>
+      </c>
+      <c r="B13" s="72">
         <v>-2.3E-2</v>
       </c>
-      <c r="C13" s="74">
+      <c r="C13" s="72">
         <v>-2.4E-2</v>
       </c>
-      <c r="D13" s="74">
+      <c r="D13" s="72">
         <v>-3.6999999999999998E-2</v>
       </c>
-      <c r="E13" s="74">
+      <c r="E13" s="72">
         <v>-3.7999999999999999E-2</v>
       </c>
-      <c r="F13" s="74">
+      <c r="F13" s="72">
         <v>-5.0999999999999997E-2</v>
       </c>
-      <c r="G13" s="74">
+      <c r="G13" s="72">
         <v>-0.05</v>
       </c>
-      <c r="H13" s="74">
+      <c r="H13" s="72">
         <v>-6.8000000000000005E-2</v>
       </c>
-      <c r="I13" s="74">
+      <c r="I13" s="72">
         <v>-6.9000000000000006E-2</v>
       </c>
-      <c r="J13" s="74">
+      <c r="J13" s="72">
         <v>-8.4000000000000005E-2</v>
       </c>
-      <c r="K13" s="74">
+      <c r="K13" s="72">
         <v>-8.2000000000000003E-2</v>
       </c>
     </row>
@@ -5615,17 +5412,17 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B3" s="69" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3" s="69" t="s">
-        <v>172</v>
-      </c>
-      <c r="D3" s="69" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="69" t="s">
-        <v>178</v>
+      <c r="B3" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>176</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>80</v>
@@ -5647,412 +5444,488 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="68" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="70" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="74">
+        <v>7.2659999999999999E-3</v>
+      </c>
+      <c r="I4" s="74"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B5" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G5" s="70" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="74">
+        <v>7.4250000000000002E-3</v>
+      </c>
+      <c r="I5" s="74"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B6" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>199</v>
+      </c>
+      <c r="H6" s="74">
+        <v>6.2570000000000004E-3</v>
+      </c>
+      <c r="I6" s="74"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B7" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" s="70" t="s">
+        <v>200</v>
+      </c>
+      <c r="H7" s="74">
+        <v>3.5969999999999999E-3</v>
+      </c>
+      <c r="I7" s="74"/>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B8" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="70" t="s">
+        <v>201</v>
+      </c>
+      <c r="H8" s="74">
+        <v>7.0569999999999999E-3</v>
+      </c>
+      <c r="I8" s="74"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B9" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C9" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="H9" s="74">
+        <v>2.2829999999999999E-3</v>
+      </c>
+      <c r="I9" s="74"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B10" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="70" t="s">
+        <v>203</v>
+      </c>
+      <c r="H10" s="74">
+        <v>2.6779999999999998E-3</v>
+      </c>
+      <c r="I10" s="74"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B11" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="H11" s="74">
+        <v>6.698E-3</v>
+      </c>
+      <c r="I11" s="74"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B12" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G12" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="H12" s="74">
+        <v>1.761E-3</v>
+      </c>
+      <c r="I12" s="74"/>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B13" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G13" s="70" t="s">
+        <v>206</v>
+      </c>
+      <c r="H13" s="74">
+        <v>4.2830000000000003E-3</v>
+      </c>
+      <c r="I13" s="74"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B14" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G14" s="70" t="s">
+        <v>207</v>
+      </c>
+      <c r="H14" s="74">
+        <v>5.195E-3</v>
+      </c>
+      <c r="I14" s="74"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B15" s="68" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="D4" s="70" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" s="72" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B5" s="70" t="s">
+      <c r="D15" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G15" s="70" t="s">
+        <v>208</v>
+      </c>
+      <c r="H15" s="74">
+        <v>6.7330000000000003E-3</v>
+      </c>
+      <c r="I15" s="74"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B16" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G16" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="H16" s="74">
+        <v>8.1720000000000004E-3</v>
+      </c>
+      <c r="I16" s="74"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B17" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="68" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="70" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G5" s="72" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B6" s="70" t="s">
+      <c r="D17" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>210</v>
+      </c>
+      <c r="H17" s="74">
+        <v>3.4849999999999998E-3</v>
+      </c>
+      <c r="I17" s="74"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B18" s="68" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="E18" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G18" s="70" t="s">
+        <v>211</v>
+      </c>
+      <c r="H18" s="74">
+        <v>7.3709999999999999E-3</v>
+      </c>
+      <c r="I18" s="74"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B19" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="70" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>182</v>
-      </c>
-      <c r="E6" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G6" s="72" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B7" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="D7" s="70" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G7" s="72" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B8" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="70" t="s">
-        <v>184</v>
-      </c>
-      <c r="E8" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G8" s="72" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B9" s="70" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="70" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="72" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B10" s="70" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="70" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="70" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G10" s="72" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B11" s="70" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" s="70" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="70" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G11" s="72" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B12" s="70" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" s="70" t="s">
-        <v>188</v>
-      </c>
-      <c r="E12" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G12" s="72" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B13" s="70" t="s">
-        <v>151</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>152</v>
-      </c>
-      <c r="D13" s="70" t="s">
-        <v>189</v>
-      </c>
-      <c r="E13" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G13" s="72" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B14" s="70" t="s">
+      <c r="D19" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="E19" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G19" s="70" t="s">
+        <v>212</v>
+      </c>
+      <c r="H19" s="74">
+        <v>2.271E-3</v>
+      </c>
+      <c r="I19" s="74"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B20" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C20" s="68" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="70" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G14" s="72" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B15" s="70" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="D15" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="E15" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G15" s="72" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B16" s="70" t="s">
-        <v>170</v>
-      </c>
-      <c r="C16" s="70" t="s">
-        <v>176</v>
-      </c>
-      <c r="D16" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G16" s="72" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B17" s="70" t="s">
+      <c r="D20" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G20" s="70" t="s">
+        <v>213</v>
+      </c>
+      <c r="H20" s="74">
+        <v>4.1650000000000003E-3</v>
+      </c>
+      <c r="I20" s="74"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B21" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C21" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="70" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G17" s="72" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B18" s="70" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="70" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="E18" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G18" s="72" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B19" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="70" t="s">
-        <v>140</v>
-      </c>
-      <c r="D19" s="70" t="s">
+      <c r="D21" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="E19" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G19" s="72" t="s">
+      <c r="E21" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G21" s="70" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B20" s="70" t="s">
+      <c r="H21" s="74">
+        <v>2.9269999999999999E-3</v>
+      </c>
+      <c r="I21" s="74"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B22" s="68" t="s">
         <v>147</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C22" s="68" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="70" t="s">
+      <c r="D22" s="68" t="s">
         <v>196</v>
       </c>
-      <c r="E20" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G20" s="72" t="s">
+      <c r="E22" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G22" s="70" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B21" s="70" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="70" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="70" t="s">
-        <v>197</v>
-      </c>
-      <c r="E21" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G21" s="72" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B22" s="70" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="70" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G22" s="72" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B28" s="71"/>
-      <c r="C28" s="70"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B29" s="71"/>
-      <c r="C29" s="70"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B30" s="71"/>
-      <c r="C30" s="70"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B31" s="71"/>
-      <c r="C31" s="70"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B32" s="71"/>
-      <c r="C32" s="70"/>
+      <c r="H22" s="74">
+        <v>6.1450000000000003E-3</v>
+      </c>
+      <c r="I22" s="74"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B28" s="69"/>
+      <c r="C28" s="68"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B29" s="69"/>
+      <c r="C29" s="68"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B30" s="69"/>
+      <c r="C30" s="68"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B31" s="69"/>
+      <c r="C31" s="68"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B32" s="69"/>
+      <c r="C32" s="68"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B33" s="71"/>
-      <c r="C33" s="70"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="68"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B34" s="71"/>
-      <c r="C34" s="70"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="68"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B35" s="71"/>
-      <c r="C35" s="70"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="68"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B36" s="71"/>
-      <c r="C36" s="70"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="68"/>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B37" s="71"/>
-      <c r="C37" s="70"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="68"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B38" s="71"/>
-      <c r="C38" s="70"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="68"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B39" s="71"/>
-      <c r="C39" s="70"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="68"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B40" s="71"/>
-      <c r="C40" s="70"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="68"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B41" s="71"/>
-      <c r="C41" s="70"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="68"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B42" s="71"/>
-      <c r="C42" s="70"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="68"/>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B43" s="71"/>
-      <c r="C43" s="70"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="68"/>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B44" s="71"/>
-      <c r="C44" s="70"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="68"/>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B45" s="71"/>
-      <c r="C45" s="70"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="68"/>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B46" s="71"/>
-      <c r="C46" s="70"/>
+      <c r="B46" s="69"/>
+      <c r="C46" s="68"/>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B47" s="71"/>
-      <c r="C47" s="70"/>
+      <c r="B47" s="69"/>
+      <c r="C47" s="68"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:D3" xr:uid="{6343D198-108B-4166-BADD-64B947BEDED9}">
@@ -6061,6 +5934,7 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6095,12 +5969,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="28c4117a-bbb3-4e1f-8a90-b630a637c5f5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b6f0f157-b05d-47b5-a4ad-9104388b9e00">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6370,20 +6246,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="28c4117a-bbb3-4e1f-8a90-b630a637c5f5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b6f0f157-b05d-47b5-a4ad-9104388b9e00">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39299E98-CCB7-43FF-A59F-E13BC180F587}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A569D96-EBC1-4F05-A274-F7D34647513F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="28c4117a-bbb3-4e1f-8a90-b630a637c5f5"/>
+    <ds:schemaRef ds:uri="b6f0f157-b05d-47b5-a4ad-9104388b9e00"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6409,12 +6286,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A569D96-EBC1-4F05-A274-F7D34647513F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39299E98-CCB7-43FF-A59F-E13BC180F587}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="28c4117a-bbb3-4e1f-8a90-b630a637c5f5"/>
-    <ds:schemaRef ds:uri="b6f0f157-b05d-47b5-a4ad-9104388b9e00"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
